--- a/Matriz_Layout_Camara__con_propuesta_G4.xlsx
+++ b/Matriz_Layout_Camara__con_propuesta_G4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\OPERACIONES\PROYECTOS VIGENTES\HELACOR\HELACOR - GESTIÓN DE EXCELENCIA\Gestión de Excelencia\PDCA y PILOTO 17 franquicias\LEAN en Franquicias\Franquicia\Velez Sarsfield 3300\Tarjetas Kanban\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AAD621-D9E2-4482-AD1F-7D8469587621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4D2177-D6D1-4AE2-BD39-B4C26695C417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="489">
   <si>
     <t>Categoría_ID_Actual</t>
   </si>
@@ -1961,9 +1961,6 @@
     <t>P[2-3]</t>
   </si>
   <si>
-    <t>P[1-2]</t>
-  </si>
-  <si>
     <t>Kw_h/kg almacenado Producto</t>
   </si>
   <si>
@@ -1998,6 +1995,42 @@
   </si>
   <si>
     <t>CAMARA</t>
+  </si>
+  <si>
+    <t>FRIZZIO PIZZA JAMON Y QUESO</t>
+  </si>
+  <si>
+    <t>FRIZZIO PIZZA INTEGRAL</t>
+  </si>
+  <si>
+    <t>FRIZZIO PIZZA MUZZA</t>
+  </si>
+  <si>
+    <t>FROODIE WRAPS</t>
+  </si>
+  <si>
+    <t>FRIZZIO MINI PIZZA</t>
+  </si>
+  <si>
+    <t>PECHUGUITAS</t>
+  </si>
+  <si>
+    <t>BASTONCITOS</t>
+  </si>
+  <si>
+    <t>EMPANADAS JAMON Y QUESO / CARNE</t>
+  </si>
+  <si>
+    <t>FRIZZIO PIZZA CASERA</t>
+  </si>
+  <si>
+    <t>FRIZZIO PIZZA CEBOLLA</t>
+  </si>
+  <si>
+    <t>CCC</t>
+  </si>
+  <si>
+    <t>FROODIE</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2050,7 @@
     <numFmt numFmtId="173" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="174" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2323,18 +2356,22 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2553,11 +2590,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3045,29 +3083,41 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="43" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3086,10 +3136,23 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="45" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="45" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -4087,7 +4150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ1048576"/>
+  <dimension ref="A1:BC1048576"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -4138,13 +4201,13 @@
   <sheetData>
     <row r="1" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -4234,7 +4297,7 @@
         <v>25</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AH1" s="3" t="s">
         <v>26</v>
@@ -4269,10 +4332,10 @@
     </row>
     <row r="2" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C2" s="1">
         <f>+J2</f>
@@ -4323,7 +4386,7 @@
         <v>1.04E-2</v>
       </c>
       <c r="R2" s="5">
-        <f t="shared" ref="R2:R26" si="0">+N2/Q2</f>
+        <f t="shared" ref="R2:R34" si="0">+N2/Q2</f>
         <v>750</v>
       </c>
       <c r="S2" s="5">
@@ -4334,7 +4397,7 @@
         <v>5871.9975570000006</v>
       </c>
       <c r="U2" s="8">
-        <f t="shared" ref="U2:U26" si="1">+Q2*S2</f>
+        <f t="shared" ref="U2:U34" si="1">+Q2*S2</f>
         <v>1.6639999999999999</v>
       </c>
       <c r="V2" s="5">
@@ -4347,11 +4410,11 @@
         <v>14.21</v>
       </c>
       <c r="Y2" s="10">
-        <f t="shared" ref="Y2:Y26" si="2">+V2/X2</f>
+        <f t="shared" ref="Y2:Y36" si="2">+V2/X2</f>
         <v>0.11400422237860662</v>
       </c>
       <c r="Z2" s="10">
-        <f t="shared" ref="Z2:Z26" si="3">+U2/W2</f>
+        <f t="shared" ref="Z2:Z36" si="3">+U2/W2</f>
         <v>0.61402214022140222</v>
       </c>
       <c r="AA2" s="9">
@@ -4387,19 +4450,19 @@
       </c>
       <c r="AI2" s="16">
         <f t="shared" ref="AI2:AI26" si="7">+O2/$O$1048576</f>
-        <v>0.30052317038459747</v>
+        <v>0.29569900116289316</v>
       </c>
       <c r="AJ2" s="10"/>
       <c r="AK2" s="10"/>
     </row>
     <row r="3" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="190" t="s">
-        <v>468</v>
-      </c>
-      <c r="B3" s="191" t="s">
-        <v>477</v>
-      </c>
-      <c r="C3" s="191">
+      <c r="A3" s="184" t="s">
+        <v>467</v>
+      </c>
+      <c r="B3" s="185" t="s">
+        <v>476</v>
+      </c>
+      <c r="C3" s="185">
         <f t="shared" ref="C3:C27" si="8">+J3</f>
         <v>5</v>
       </c>
@@ -4514,7 +4577,7 @@
       </c>
       <c r="AI3" s="29">
         <f t="shared" si="7"/>
-        <v>0.21036621926921825</v>
+        <v>0.2069893008140252</v>
       </c>
       <c r="AJ3" s="30">
         <v>0.51</v>
@@ -4548,10 +4611,10 @@
     </row>
     <row r="4" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="8"/>
@@ -4671,17 +4734,17 @@
       </c>
       <c r="AI4" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
+        <v>1.0235734655638609E-2</v>
       </c>
       <c r="AJ4" s="10"/>
       <c r="AK4" s="10"/>
     </row>
     <row r="5" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="8"/>
@@ -4801,17 +4864,17 @@
       </c>
       <c r="AI5" s="16">
         <f t="shared" si="7"/>
-        <v>3.929918381952429E-3</v>
+        <v>3.8668330921301413E-3</v>
       </c>
       <c r="AJ5" s="10"/>
       <c r="AK5" s="10"/>
     </row>
     <row r="6" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="8"/>
@@ -4931,17 +4994,17 @@
       </c>
       <c r="AI6" s="16">
         <f t="shared" si="7"/>
-        <v>3.4675750428992021E-3</v>
+        <v>3.4119115518795361E-3</v>
       </c>
       <c r="AJ6" s="10"/>
       <c r="AK6" s="10"/>
     </row>
     <row r="7" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="8"/>
@@ -5061,15 +5124,15 @@
       </c>
       <c r="AI7" s="16">
         <f t="shared" si="7"/>
-        <v>3.8836840480471063E-3</v>
+        <v>3.8213409381050805E-3</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="8"/>
@@ -5189,15 +5252,15 @@
       </c>
       <c r="AI8" s="16">
         <f t="shared" si="7"/>
-        <v>8.5533517724846984E-3</v>
+        <v>8.4160484946361903E-3</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="8"/>
@@ -5317,15 +5380,15 @@
       </c>
       <c r="AI9" s="16">
         <f t="shared" si="7"/>
-        <v>2.6199455879682859E-3</v>
+        <v>2.577888728086761E-3</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="8"/>
@@ -5445,15 +5508,15 @@
       </c>
       <c r="AI10" s="16">
         <f t="shared" si="7"/>
-        <v>2.3117166952661347E-3</v>
+        <v>2.2746077012530241E-3</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="8"/>
@@ -5573,15 +5636,15 @@
       </c>
       <c r="AI11" s="16">
         <f t="shared" si="7"/>
-        <v>8.9001092767746186E-3</v>
+        <v>8.7572396498241424E-3</v>
       </c>
     </row>
     <row r="12" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="8"/>
@@ -5701,15 +5764,15 @@
       </c>
       <c r="AI12" s="16">
         <f t="shared" si="7"/>
-        <v>7.1952182140158439E-3</v>
+        <v>7.0797164701500376E-3</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="8"/>
@@ -5750,7 +5813,7 @@
         <v>9.6000000000000014</v>
       </c>
       <c r="O13" s="51">
-        <f t="shared" ref="O13:O26" si="18">+N13*M13</f>
+        <f t="shared" ref="O13:O36" si="18">+N13*M13</f>
         <v>43.2</v>
       </c>
       <c r="P13" s="39">
@@ -5829,15 +5892,15 @@
       </c>
       <c r="AI13" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
+        <v>1.0235734655638609E-2</v>
       </c>
     </row>
     <row r="14" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="8"/>
@@ -5957,15 +6020,15 @@
       </c>
       <c r="AI14" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
+        <v>1.0235734655638609E-2</v>
       </c>
     </row>
     <row r="15" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="8"/>
@@ -6085,15 +6148,15 @@
       </c>
       <c r="AI15" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
+        <v>1.0235734655638609E-2</v>
       </c>
     </row>
     <row r="16" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="8"/>
@@ -6213,15 +6276,15 @@
       </c>
       <c r="AI16" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1.0235734655638609E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="8"/>
@@ -6341,15 +6404,15 @@
       </c>
       <c r="AI17" s="16">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1.0235734655638609E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="52" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C18" s="56">
         <f t="shared" si="8"/>
@@ -6469,7 +6532,7 @@
       </c>
       <c r="AI18" s="29">
         <f t="shared" si="7"/>
-        <v>1.0402725128697606E-2</v>
+        <v>1.0235734655638609E-2</v>
       </c>
       <c r="AJ18" s="61">
         <v>0.2</v>
@@ -6501,12 +6564,12 @@
         <v>4.4593792642528982E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="8"/>
@@ -6624,16 +6687,16 @@
       </c>
       <c r="AI19" s="67">
         <f t="shared" si="7"/>
-        <v>5.38341025410101E-2</v>
+        <v>5.2969926842929796E-2</v>
       </c>
       <c r="AQ19" s="1"/>
     </row>
-    <row r="20" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="52" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C20" s="56">
         <f t="shared" si="8"/>
@@ -6751,7 +6814,7 @@
       </c>
       <c r="AI20" s="29">
         <f t="shared" si="7"/>
-        <v>7.1778803388013471E-2</v>
+        <v>7.0626569123906399E-2</v>
       </c>
       <c r="AJ20" s="61">
         <v>8.77E-2</v>
@@ -6783,12 +6846,12 @@
         <v>6.668834140758316E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="8"/>
@@ -6833,7 +6896,7 @@
       </c>
       <c r="P21" s="39">
         <f>+$AO$26*O21/SUM($O$21:$O$26)</f>
-        <v>507.244638255756</v>
+        <v>536.42283900679809</v>
       </c>
       <c r="Q21" s="1">
         <f>+(39*25*26)/1000000</f>
@@ -6848,7 +6911,7 @@
       </c>
       <c r="T21" s="39">
         <f>+$AO$26*S21/SUM($S$21:$S$26)</f>
-        <v>531.54626774309997</v>
+        <v>559.52238709799997</v>
       </c>
       <c r="U21" s="44">
         <f t="shared" si="1"/>
@@ -6905,18 +6968,18 @@
       </c>
       <c r="AI21" s="16">
         <f t="shared" si="7"/>
-        <v>7.9465261399773376E-2</v>
+        <v>7.8189639730572705E-2</v>
       </c>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="78"/>
       <c r="AL21" s="1"/>
     </row>
-    <row r="22" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="8"/>
@@ -6961,7 +7024,7 @@
       </c>
       <c r="P22" s="39">
         <f t="shared" ref="P22:P26" si="22">+$AO$26*O22/SUM($O$21:$O$26)</f>
-        <v>73.781038291746341</v>
+        <v>78.025140219170638</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" ref="Q22:Q23" si="23">+(39*25*26)/1000000</f>
@@ -6976,7 +7039,7 @@
       </c>
       <c r="T22" s="39">
         <f t="shared" ref="T22:T26" si="24">+$AO$26*S22/SUM($S$21:$S$26)</f>
-        <v>106.30925354862001</v>
+        <v>111.90447741960001</v>
       </c>
       <c r="U22" s="44">
         <f t="shared" si="1"/>
@@ -7012,7 +7075,7 @@
         <v>77.520035158282013</v>
       </c>
       <c r="AD22" s="13">
-        <f t="shared" ref="AD22:AD26" si="26">(2.09*2.94*0.75+1.2*1.6*2.09)/AA22*AB22*$AN$26</f>
+        <f t="shared" ref="AD22:AD36" si="26">(2.09*2.94*0.75+1.2*1.6*2.09)/AA22*AB22*$AN$26</f>
         <v>19.596516628792486</v>
       </c>
       <c r="AE22" s="12">
@@ -7033,25 +7096,25 @@
       </c>
       <c r="AI22" s="67">
         <f t="shared" si="7"/>
-        <v>1.1558583476330674E-2</v>
+        <v>1.137303850626512E-2</v>
       </c>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="78"/>
       <c r="AL22" s="1"/>
     </row>
-    <row r="23" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>37</v>
@@ -7089,7 +7152,7 @@
       </c>
       <c r="P23" s="39">
         <f t="shared" si="22"/>
-        <v>290.05170678442772</v>
+        <v>306.73633248661451</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="23"/>
@@ -7104,7 +7167,7 @@
       </c>
       <c r="T23" s="39">
         <f t="shared" si="24"/>
-        <v>327.78686510824502</v>
+        <v>345.0388053771</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="1"/>
@@ -7161,18 +7224,18 @@
       </c>
       <c r="AI23" s="67">
         <f t="shared" si="7"/>
-        <v>4.5439681291324953E-2</v>
+        <v>4.4710257627754754E-2</v>
       </c>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="78"/>
       <c r="AL23" s="1"/>
     </row>
-    <row r="24" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>454</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="8"/>
@@ -7206,18 +7269,18 @@
         <v>4</v>
       </c>
       <c r="M24" s="37">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N24" s="1">
         <v>6.27</v>
       </c>
       <c r="O24" s="178">
         <f t="shared" si="18"/>
-        <v>169.29</v>
+        <v>112.85999999999999</v>
       </c>
       <c r="P24" s="39">
         <f t="shared" si="22"/>
-        <v>260.21649942520281</v>
+        <v>183.45661094032494</v>
       </c>
       <c r="Q24" s="40">
         <f>+(45*23*21.5)/1000000</f>
@@ -7228,15 +7291,15 @@
         <v>281.76609369733734</v>
       </c>
       <c r="S24" s="37">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="T24" s="39">
         <f t="shared" si="24"/>
-        <v>239.195820484395</v>
+        <v>167.85671612940001</v>
       </c>
       <c r="U24" s="44">
         <f t="shared" si="1"/>
-        <v>0.6008175</v>
+        <v>0.40054500000000004</v>
       </c>
       <c r="V24" s="1">
         <f>+(0.75*1.02)</f>
@@ -7252,9 +7315,9 @@
         <f t="shared" si="2"/>
         <v>5.3835327234342013E-2</v>
       </c>
-      <c r="Z24" s="189">
+      <c r="Z24" s="46">
         <f t="shared" si="3"/>
-        <v>1.1219747899159664</v>
+        <v>0.747983193277311</v>
       </c>
       <c r="AA24" s="37">
         <v>34.103999999999999</v>
@@ -7281,23 +7344,23 @@
       </c>
       <c r="AG24" s="14">
         <f t="shared" si="6"/>
-        <v>0.5736697488751521</v>
+        <v>0.86050462331272826</v>
       </c>
       <c r="AH24" s="15">
         <f t="shared" si="28"/>
-        <v>0.18529532888667413</v>
+        <v>0.27794299333001121</v>
       </c>
       <c r="AI24" s="67">
         <f t="shared" si="7"/>
-        <v>4.0765679098083742E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2.6740856787855861E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>453</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="8"/>
@@ -7342,7 +7405,7 @@
       </c>
       <c r="P25" s="39">
         <f t="shared" si="22"/>
-        <v>79.683521355086029</v>
+        <v>84.267151436704282</v>
       </c>
       <c r="Q25" s="40">
         <f>+(31.5*21.5*24.5)/1000000</f>
@@ -7357,7 +7420,7 @@
       </c>
       <c r="T25" s="39">
         <f t="shared" si="24"/>
-        <v>159.46388032293001</v>
+        <v>167.85671612940001</v>
       </c>
       <c r="U25" s="44">
         <f t="shared" si="1"/>
@@ -7414,15 +7477,15 @@
       </c>
       <c r="AI25" s="67">
         <f t="shared" si="7"/>
-        <v>1.2483270154437126E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1.2282881586766329E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="52" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C26" s="56">
         <f t="shared" si="8"/>
@@ -7452,7 +7515,7 @@
       <c r="K26" s="56">
         <v>3</v>
       </c>
-      <c r="L26" s="188" t="s">
+      <c r="L26" s="183" t="s">
         <v>464</v>
       </c>
       <c r="M26" s="53">
@@ -7467,7 +7530,7 @@
       </c>
       <c r="P26" s="57">
         <f t="shared" si="22"/>
-        <v>383.66139911708092</v>
+        <v>405.7307291396873</v>
       </c>
       <c r="Q26" s="56">
         <f t="shared" ref="Q26" si="29">39*20*30/1000000</f>
@@ -7482,7 +7545,7 @@
       </c>
       <c r="T26" s="57">
         <f t="shared" si="24"/>
-        <v>230.33671602201002</v>
+        <v>242.45970107580001</v>
       </c>
       <c r="U26" s="58">
         <f t="shared" si="1"/>
@@ -7539,7 +7602,7 @@
       </c>
       <c r="AI26" s="29">
         <f t="shared" si="7"/>
-        <v>6.0104634076919496E-2</v>
+        <v>5.9139800232578629E-2</v>
       </c>
       <c r="AJ26" s="61">
         <f>0.074+0.00747</f>
@@ -7573,96 +7636,3023 @@
         <v>3.6045457551898544E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>452</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="D27" s="183" t="s">
+      <c r="D27" s="189" t="s">
+        <v>477</v>
+      </c>
+      <c r="E27" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="188" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J27" s="188">
+        <v>3</v>
+      </c>
+      <c r="K27" s="188">
+        <v>3</v>
+      </c>
+      <c r="L27" s="188">
+        <v>2</v>
+      </c>
+      <c r="M27" s="188">
+        <v>4</v>
+      </c>
+      <c r="N27" s="190">
+        <f>535*11/1000</f>
+        <v>5.8849999999999998</v>
+      </c>
+      <c r="O27" s="178">
+        <f t="shared" si="18"/>
+        <v>23.54</v>
+      </c>
+      <c r="P27" s="39">
+        <f t="shared" ref="P27:P35" si="30">+$AO$36*O27/SUM($O$27:$O$36)</f>
+        <v>109.0854292494318</v>
+      </c>
+      <c r="Q27" s="188">
+        <f>30*32*28.5/1000000</f>
+        <v>2.7359999999999999E-2</v>
+      </c>
+      <c r="R27" s="64">
+        <f t="shared" si="0"/>
+        <v>215.09502923976609</v>
+      </c>
+      <c r="S27" s="188">
+        <v>4</v>
+      </c>
+      <c r="T27" s="39">
+        <f t="shared" ref="T27:T35" si="31">+$AO$36*S27/SUM($S$27:$S$36)</f>
+        <v>100.07926271060869</v>
+      </c>
+      <c r="U27" s="44">
+        <f t="shared" si="1"/>
+        <v>0.10944</v>
+      </c>
+      <c r="V27" s="188">
+        <f>30*32/10000</f>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W27" s="188">
+        <f>1.37*1.02*0.7/6</f>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X27" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y27" s="67">
+        <f t="shared" si="2"/>
+        <v>6.7558057705840958E-3</v>
+      </c>
+      <c r="Z27" s="46">
+        <f t="shared" si="3"/>
+        <v>0.67128749309942948</v>
+      </c>
+      <c r="AA27" s="186">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB27" s="11">
+        <f t="shared" ref="AB27:AB36" si="32">+W27/AA27</f>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC27" s="12">
+        <f t="shared" ref="AC27:AC36" si="33">+$AN$26*AB27</f>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD27" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE27" s="12">
+        <f t="shared" ref="AE27:AE36" si="34">+AC27+AD27</f>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF27" s="12">
+        <f t="shared" ref="AF27:AF36" si="35">+$AP$26*AE27</f>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG27" s="14">
+        <f t="shared" ref="AG27:AG36" si="36">+AE27/O27</f>
+        <v>1.2560150660652516</v>
+      </c>
+      <c r="AH27" s="15">
+        <f t="shared" ref="AH27:AH36" si="37">+AG27*$AP$26</f>
+        <v>0.40569286633907625</v>
+      </c>
+      <c r="AI27" s="16">
+        <f t="shared" ref="AI27:AI36" si="38">+O27/$O$1048576</f>
+        <v>5.5775276341141862E-3</v>
+      </c>
+      <c r="AJ27" s="189"/>
+      <c r="AK27" s="189"/>
+      <c r="AL27" s="189"/>
+      <c r="AM27" s="189"/>
+      <c r="AN27" s="189"/>
+      <c r="AO27" s="189"/>
+      <c r="AP27" s="189"/>
+      <c r="AQ27" s="189"/>
+      <c r="AR27" s="189"/>
+      <c r="AS27" s="189"/>
+      <c r="AT27" s="189"/>
+      <c r="AU27" s="189"/>
+      <c r="AV27" s="189"/>
+      <c r="AW27" s="189"/>
+      <c r="AX27" s="189"/>
+      <c r="AY27" s="189"/>
+      <c r="AZ27" s="189"/>
+      <c r="BA27" s="189"/>
+      <c r="BB27" s="189"/>
+      <c r="BC27" s="189"/>
+    </row>
+    <row r="28" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>452</v>
       </c>
-      <c r="E27" s="183"/>
-      <c r="F27" s="183"/>
-      <c r="G27" s="183"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="184" t="s">
+      <c r="B28" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>479</v>
+      </c>
+      <c r="E28" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="187" t="s">
         <v>68</v>
       </c>
-      <c r="J27" s="185">
+      <c r="J28" s="1">
         <v>3</v>
       </c>
-      <c r="K27" s="185">
+      <c r="K28" s="1">
         <v>3</v>
       </c>
-      <c r="L27" s="186" t="s">
-        <v>465</v>
-      </c>
-      <c r="M27" s="183"/>
-      <c r="N27" s="183"/>
-      <c r="O27" s="183"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="183"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="183"/>
-      <c r="U27" s="183"/>
-      <c r="V27" s="185">
-        <v>1.34</v>
-      </c>
-      <c r="W27" s="185">
-        <f>+V27*0.7</f>
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="X27" s="187">
+      <c r="L28" s="1">
+        <v>3</v>
+      </c>
+      <c r="M28" s="188">
+        <v>4</v>
+      </c>
+      <c r="N28" s="188">
+        <f>12*510/1000</f>
+        <v>6.12</v>
+      </c>
+      <c r="O28" s="178">
+        <f t="shared" si="18"/>
+        <v>24.48</v>
+      </c>
+      <c r="P28" s="39">
+        <f t="shared" si="30"/>
+        <v>113.44143194673282</v>
+      </c>
+      <c r="Q28" s="188">
+        <f t="shared" ref="Q28:Q31" si="39">30*32*28.5/1000000</f>
+        <v>2.7359999999999999E-2</v>
+      </c>
+      <c r="R28" s="64">
+        <f t="shared" si="0"/>
+        <v>223.68421052631581</v>
+      </c>
+      <c r="S28" s="188">
+        <v>4</v>
+      </c>
+      <c r="T28" s="39">
+        <f t="shared" si="31"/>
+        <v>100.07926271060869</v>
+      </c>
+      <c r="U28" s="44">
+        <f t="shared" si="1"/>
+        <v>0.10944</v>
+      </c>
+      <c r="V28" s="188">
+        <f t="shared" ref="V28:V31" si="40">30*32/10000</f>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W28" s="188">
+        <f t="shared" ref="W28:W36" si="41">1.37*1.02*0.7/6</f>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X28" s="186">
         <v>14.21</v>
       </c>
-      <c r="Y27" s="183"/>
-      <c r="Z27" s="183"/>
-      <c r="AA27" s="37">
+      <c r="Y28" s="67">
+        <f t="shared" si="2"/>
+        <v>6.7558057705840958E-3</v>
+      </c>
+      <c r="Z28" s="46">
+        <f t="shared" si="3"/>
+        <v>0.67128749309942948</v>
+      </c>
+      <c r="AA28" s="188">
         <v>34.103999999999999</v>
       </c>
-      <c r="AB27" s="183"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="183"/>
-      <c r="AE27" s="183"/>
-      <c r="AF27" s="183"/>
-      <c r="AG27" s="183"/>
-      <c r="AH27" s="183"/>
-      <c r="AI27" s="183"/>
-      <c r="AJ27" s="183"/>
-      <c r="AK27" s="183"/>
-      <c r="AL27" s="183"/>
-      <c r="AM27" s="183"/>
-      <c r="AN27" s="183"/>
-      <c r="AO27" s="183"/>
-      <c r="AP27" s="183"/>
-      <c r="AQ27" s="183"/>
-    </row>
-    <row r="28" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-    </row>
-    <row r="29" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-    </row>
-    <row r="30" spans="1:43" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="AB28" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC28" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD28" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE28" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF28" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG28" s="14">
+        <f t="shared" si="36"/>
+        <v>1.2077857293781054</v>
+      </c>
+      <c r="AH28" s="15">
+        <f t="shared" si="37"/>
+        <v>0.39011479058912801</v>
+      </c>
+      <c r="AI28" s="67">
+        <f t="shared" si="38"/>
+        <v>5.8002496381952115E-3</v>
+      </c>
+      <c r="AJ28" s="189"/>
+      <c r="AK28" s="189"/>
+      <c r="AL28" s="189"/>
+      <c r="AM28" s="189"/>
+      <c r="AN28" s="189"/>
+      <c r="AO28" s="189"/>
+      <c r="AP28" s="189"/>
+      <c r="AQ28" s="189"/>
+      <c r="AR28" s="189"/>
+      <c r="AS28" s="189"/>
+      <c r="AT28" s="189"/>
+      <c r="AU28" s="189"/>
+      <c r="AV28" s="189"/>
+      <c r="AW28" s="189"/>
+      <c r="AX28" s="189"/>
+      <c r="AY28" s="189"/>
+      <c r="AZ28" s="189"/>
+      <c r="BA28" s="189"/>
+      <c r="BB28" s="189"/>
+      <c r="BC28" s="189"/>
+    </row>
+    <row r="29" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>452</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>485</v>
+      </c>
+      <c r="E29" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" s="1">
+        <v>3</v>
+      </c>
+      <c r="K29" s="1">
+        <v>3</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="188">
+        <v>2</v>
+      </c>
+      <c r="N29" s="188">
+        <f>8*665/1000</f>
+        <v>5.32</v>
+      </c>
+      <c r="O29" s="178">
+        <f t="shared" si="18"/>
+        <v>10.64</v>
+      </c>
+      <c r="P29" s="39">
+        <f t="shared" si="30"/>
+        <v>49.306243297109368</v>
+      </c>
+      <c r="Q29" s="188">
+        <f t="shared" si="39"/>
+        <v>2.7359999999999999E-2</v>
+      </c>
+      <c r="R29" s="64">
+        <f t="shared" si="0"/>
+        <v>194.44444444444446</v>
+      </c>
+      <c r="S29" s="188">
+        <v>2</v>
+      </c>
+      <c r="T29" s="39">
+        <f t="shared" si="31"/>
+        <v>50.039631355304344</v>
+      </c>
+      <c r="U29" s="44">
+        <f t="shared" si="1"/>
+        <v>5.4719999999999998E-2</v>
+      </c>
+      <c r="V29" s="188">
+        <f t="shared" si="40"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W29" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X29" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y29" s="67">
+        <f t="shared" si="2"/>
+        <v>6.7558057705840958E-3</v>
+      </c>
+      <c r="Z29" s="46">
+        <f t="shared" si="3"/>
+        <v>0.33564374654971474</v>
+      </c>
+      <c r="AA29" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB29" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC29" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD29" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE29" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF29" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG29" s="14">
+        <f t="shared" si="36"/>
+        <v>2.7788152871406036</v>
+      </c>
+      <c r="AH29" s="15">
+        <f t="shared" si="37"/>
+        <v>0.897557337746415</v>
+      </c>
+      <c r="AI29" s="67">
+        <f t="shared" si="38"/>
+        <v>2.5210235355554353E-3</v>
+      </c>
+      <c r="AJ29" s="189"/>
+      <c r="AK29" s="189"/>
+      <c r="AL29" s="189"/>
+      <c r="AM29" s="189"/>
+      <c r="AN29" s="189"/>
+      <c r="AO29" s="189"/>
+      <c r="AP29" s="189"/>
+      <c r="AQ29" s="189"/>
+      <c r="AR29" s="189"/>
+      <c r="AS29" s="189"/>
+      <c r="AT29" s="189"/>
+      <c r="AU29" s="189"/>
+      <c r="AV29" s="189"/>
+      <c r="AW29" s="189"/>
+      <c r="AX29" s="189"/>
+      <c r="AY29" s="189"/>
+      <c r="AZ29" s="189"/>
+      <c r="BA29" s="189"/>
+      <c r="BB29" s="189"/>
+      <c r="BC29" s="189"/>
+    </row>
+    <row r="30" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>452</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>486</v>
+      </c>
+      <c r="E30" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30" s="1">
+        <v>3</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="188">
+        <v>2</v>
+      </c>
+      <c r="N30" s="188">
+        <f>11*540/1000</f>
+        <v>5.94</v>
+      </c>
+      <c r="O30" s="178">
+        <f t="shared" si="18"/>
+        <v>11.88</v>
+      </c>
+      <c r="P30" s="39">
+        <f t="shared" si="30"/>
+        <v>55.052459621208584</v>
+      </c>
+      <c r="Q30" s="188">
+        <f t="shared" si="39"/>
+        <v>2.7359999999999999E-2</v>
+      </c>
+      <c r="R30" s="64">
+        <f t="shared" si="0"/>
+        <v>217.10526315789477</v>
+      </c>
+      <c r="S30" s="188">
+        <v>2</v>
+      </c>
+      <c r="T30" s="39">
+        <f t="shared" si="31"/>
+        <v>50.039631355304344</v>
+      </c>
+      <c r="U30" s="44">
+        <f t="shared" si="1"/>
+        <v>5.4719999999999998E-2</v>
+      </c>
+      <c r="V30" s="188">
+        <f t="shared" si="40"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W30" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X30" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y30" s="67">
+        <f t="shared" si="2"/>
+        <v>6.7558057705840958E-3</v>
+      </c>
+      <c r="Z30" s="46">
+        <f t="shared" si="3"/>
+        <v>0.33564374654971474</v>
+      </c>
+      <c r="AA30" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB30" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC30" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD30" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE30" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF30" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG30" s="14">
+        <f t="shared" si="36"/>
+        <v>2.4887705938700355</v>
+      </c>
+      <c r="AH30" s="15">
+        <f t="shared" si="37"/>
+        <v>0.80387290182002147</v>
+      </c>
+      <c r="AI30" s="67">
+        <f t="shared" si="38"/>
+        <v>2.8148270303006177E-3</v>
+      </c>
+      <c r="AJ30" s="189"/>
+      <c r="AK30" s="189"/>
+      <c r="AL30" s="189"/>
+      <c r="AM30" s="189"/>
+      <c r="AN30" s="189"/>
+      <c r="AO30" s="189"/>
+      <c r="AP30" s="189"/>
+      <c r="AQ30" s="189"/>
+      <c r="AR30" s="189"/>
+      <c r="AS30" s="189"/>
+      <c r="AT30" s="189"/>
+      <c r="AU30" s="189"/>
+      <c r="AV30" s="189"/>
+      <c r="AW30" s="189"/>
+      <c r="AX30" s="189"/>
+      <c r="AY30" s="189"/>
+      <c r="AZ30" s="189"/>
+      <c r="BA30" s="189"/>
+      <c r="BB30" s="189"/>
+      <c r="BC30" s="189"/>
+    </row>
+    <row r="31" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>452</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>478</v>
+      </c>
+      <c r="E31" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J31" s="1">
+        <v>3</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3</v>
+      </c>
+      <c r="L31" s="1">
+        <v>6</v>
+      </c>
+      <c r="M31" s="188">
+        <v>2</v>
+      </c>
+      <c r="N31" s="188">
+        <f>12*530/1000</f>
+        <v>6.36</v>
+      </c>
+      <c r="O31" s="178">
+        <f t="shared" si="18"/>
+        <v>12.72</v>
+      </c>
+      <c r="P31" s="39">
+        <f t="shared" si="30"/>
+        <v>58.94505777624353</v>
+      </c>
+      <c r="Q31" s="188">
+        <f t="shared" si="39"/>
+        <v>2.7359999999999999E-2</v>
+      </c>
+      <c r="R31" s="64">
+        <f t="shared" si="0"/>
+        <v>232.45614035087721</v>
+      </c>
+      <c r="S31" s="188">
+        <v>2</v>
+      </c>
+      <c r="T31" s="39">
+        <f t="shared" si="31"/>
+        <v>50.039631355304344</v>
+      </c>
+      <c r="U31" s="44">
+        <f t="shared" si="1"/>
+        <v>5.4719999999999998E-2</v>
+      </c>
+      <c r="V31" s="188">
+        <f t="shared" si="40"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="W31" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X31" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y31" s="67">
+        <f t="shared" si="2"/>
+        <v>6.7558057705840958E-3</v>
+      </c>
+      <c r="Z31" s="46">
+        <f t="shared" si="3"/>
+        <v>0.33564374654971474</v>
+      </c>
+      <c r="AA31" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB31" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC31" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD31" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE31" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF31" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG31" s="14">
+        <f t="shared" si="36"/>
+        <v>2.3244178188031461</v>
+      </c>
+      <c r="AH31" s="15">
+        <f t="shared" si="37"/>
+        <v>0.75078695547341623</v>
+      </c>
+      <c r="AI31" s="67">
+        <f t="shared" si="38"/>
+        <v>3.013855204160257E-3</v>
+      </c>
+      <c r="AJ31" s="189"/>
+      <c r="AK31" s="189"/>
+      <c r="AL31" s="189"/>
+      <c r="AM31" s="189"/>
+      <c r="AN31" s="189"/>
+      <c r="AO31" s="189"/>
+      <c r="AP31" s="189"/>
+      <c r="AQ31" s="189"/>
+      <c r="AR31" s="189"/>
+      <c r="AS31" s="189"/>
+      <c r="AT31" s="189"/>
+      <c r="AU31" s="189"/>
+      <c r="AV31" s="189"/>
+      <c r="AW31" s="189"/>
+      <c r="AX31" s="189"/>
+      <c r="AY31" s="189"/>
+      <c r="AZ31" s="189"/>
+      <c r="BA31" s="189"/>
+      <c r="BB31" s="189"/>
+      <c r="BC31" s="189"/>
+    </row>
+    <row r="32" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>452</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>481</v>
+      </c>
+      <c r="E32" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J32" s="1">
+        <v>3</v>
+      </c>
+      <c r="K32" s="1">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1">
+        <v>4</v>
+      </c>
+      <c r="M32" s="188">
+        <v>1</v>
+      </c>
+      <c r="N32" s="188">
+        <f>20*180/1000</f>
+        <v>3.6</v>
+      </c>
+      <c r="O32" s="178">
+        <f t="shared" si="18"/>
+        <v>3.6</v>
+      </c>
+      <c r="P32" s="39">
+        <f t="shared" si="30"/>
+        <v>16.682563521578359</v>
+      </c>
+      <c r="Q32" s="188">
+        <f>25*39.5*23/1000000</f>
+        <v>2.27125E-2</v>
+      </c>
+      <c r="R32" s="64">
+        <f t="shared" si="0"/>
+        <v>158.50302696752891</v>
+      </c>
+      <c r="S32" s="188">
+        <v>1</v>
+      </c>
+      <c r="T32" s="39">
+        <f t="shared" si="31"/>
+        <v>25.019815677652172</v>
+      </c>
+      <c r="U32" s="44">
+        <f t="shared" si="1"/>
+        <v>2.27125E-2</v>
+      </c>
+      <c r="V32" s="188">
+        <f>25*39.5/10000</f>
+        <v>9.8750000000000004E-2</v>
+      </c>
+      <c r="W32" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X32" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y32" s="67">
+        <f t="shared" si="2"/>
+        <v>6.9493314567206192E-3</v>
+      </c>
+      <c r="Z32" s="46">
+        <f t="shared" si="3"/>
+        <v>0.13931485002760227</v>
+      </c>
+      <c r="AA32" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB32" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC32" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD32" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE32" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF32" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG32" s="14">
+        <f t="shared" si="36"/>
+        <v>8.2129429597711177</v>
+      </c>
+      <c r="AH32" s="15">
+        <f t="shared" si="37"/>
+        <v>2.6527805760060712</v>
+      </c>
+      <c r="AI32" s="67">
+        <f t="shared" si="38"/>
+        <v>8.5297788796988403E-4</v>
+      </c>
+      <c r="AJ32" s="189"/>
+      <c r="AK32" s="189"/>
+      <c r="AL32" s="189"/>
+      <c r="AM32" s="189"/>
+      <c r="AN32" s="189"/>
+      <c r="AO32" s="189"/>
+      <c r="AP32" s="189"/>
+      <c r="AQ32" s="189"/>
+      <c r="AR32" s="189"/>
+      <c r="AS32" s="189"/>
+      <c r="AT32" s="189"/>
+      <c r="AU32" s="189"/>
+      <c r="AV32" s="189"/>
+      <c r="AW32" s="189"/>
+      <c r="AX32" s="189"/>
+      <c r="AY32" s="189"/>
+      <c r="AZ32" s="189"/>
+      <c r="BA32" s="189"/>
+      <c r="BB32" s="189"/>
+      <c r="BC32" s="189"/>
+    </row>
+    <row r="33" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>452</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>482</v>
+      </c>
+      <c r="E33" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G33" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J33" s="1">
+        <v>3</v>
+      </c>
+      <c r="K33" s="1">
+        <v>3</v>
+      </c>
+      <c r="L33" s="1">
+        <v>4</v>
+      </c>
+      <c r="M33" s="188">
+        <v>2</v>
+      </c>
+      <c r="N33" s="188">
+        <f>16*380/1000</f>
+        <v>6.08</v>
+      </c>
+      <c r="O33" s="178">
+        <f t="shared" si="18"/>
+        <v>12.16</v>
+      </c>
+      <c r="P33" s="39">
+        <f t="shared" si="30"/>
+        <v>56.349992339553559</v>
+      </c>
+      <c r="Q33" s="188">
+        <f t="shared" ref="Q33:Q34" si="42">25*39.5*23/1000000</f>
+        <v>2.27125E-2</v>
+      </c>
+      <c r="R33" s="64">
+        <f t="shared" si="0"/>
+        <v>267.69400110071547</v>
+      </c>
+      <c r="S33" s="188">
+        <v>2</v>
+      </c>
+      <c r="T33" s="39">
+        <f t="shared" si="31"/>
+        <v>50.039631355304344</v>
+      </c>
+      <c r="U33" s="44">
+        <f t="shared" si="1"/>
+        <v>4.5425E-2</v>
+      </c>
+      <c r="V33" s="188">
+        <f t="shared" ref="V33:V34" si="43">25*39.5/10000</f>
+        <v>9.8750000000000004E-2</v>
+      </c>
+      <c r="W33" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X33" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y33" s="67">
+        <f t="shared" si="2"/>
+        <v>6.9493314567206192E-3</v>
+      </c>
+      <c r="Z33" s="46">
+        <f t="shared" si="3"/>
+        <v>0.27862970005520454</v>
+      </c>
+      <c r="AA33" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB33" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC33" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD33" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE33" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF33" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG33" s="14">
+        <f t="shared" si="36"/>
+        <v>2.4314633762480282</v>
+      </c>
+      <c r="AH33" s="15">
+        <f t="shared" si="37"/>
+        <v>0.78536267052811315</v>
+      </c>
+      <c r="AI33" s="67">
+        <f t="shared" si="38"/>
+        <v>2.8811697549204975E-3</v>
+      </c>
+      <c r="AJ33" s="189"/>
+      <c r="AK33" s="189"/>
+      <c r="AL33" s="189"/>
+      <c r="AM33" s="189"/>
+      <c r="AN33" s="189"/>
+      <c r="AO33" s="189"/>
+      <c r="AP33" s="189"/>
+      <c r="AQ33" s="189"/>
+      <c r="AR33" s="189"/>
+      <c r="AS33" s="189"/>
+      <c r="AT33" s="189"/>
+      <c r="AU33" s="189"/>
+      <c r="AV33" s="189"/>
+      <c r="AW33" s="189"/>
+      <c r="AX33" s="189"/>
+      <c r="AY33" s="189"/>
+      <c r="AZ33" s="189"/>
+      <c r="BA33" s="189"/>
+      <c r="BB33" s="189"/>
+      <c r="BC33" s="189"/>
+    </row>
+    <row r="34" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>452</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>483</v>
+      </c>
+      <c r="E34" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G34" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J34" s="1">
+        <v>3</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>4</v>
+      </c>
+      <c r="M34" s="188">
+        <v>1</v>
+      </c>
+      <c r="N34" s="188">
+        <f>16*380/1000</f>
+        <v>6.08</v>
+      </c>
+      <c r="O34" s="178">
+        <f t="shared" si="18"/>
+        <v>6.08</v>
+      </c>
+      <c r="P34" s="39">
+        <f t="shared" si="30"/>
+        <v>28.174996169776779</v>
+      </c>
+      <c r="Q34" s="188">
+        <f t="shared" si="42"/>
+        <v>2.27125E-2</v>
+      </c>
+      <c r="R34" s="64">
+        <f t="shared" si="0"/>
+        <v>267.69400110071547</v>
+      </c>
+      <c r="S34" s="188">
+        <v>1</v>
+      </c>
+      <c r="T34" s="39">
+        <f t="shared" si="31"/>
+        <v>25.019815677652172</v>
+      </c>
+      <c r="U34" s="44">
+        <f t="shared" si="1"/>
+        <v>2.27125E-2</v>
+      </c>
+      <c r="V34" s="188">
+        <f t="shared" si="43"/>
+        <v>9.8750000000000004E-2</v>
+      </c>
+      <c r="W34" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X34" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y34" s="67">
+        <f t="shared" si="2"/>
+        <v>6.9493314567206192E-3</v>
+      </c>
+      <c r="Z34" s="46">
+        <f t="shared" si="3"/>
+        <v>0.13931485002760227</v>
+      </c>
+      <c r="AA34" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB34" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC34" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD34" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE34" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF34" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG34" s="14">
+        <f t="shared" si="36"/>
+        <v>4.8629267524960564</v>
+      </c>
+      <c r="AH34" s="15">
+        <f t="shared" si="37"/>
+        <v>1.5707253410562263</v>
+      </c>
+      <c r="AI34" s="67">
+        <f t="shared" si="38"/>
+        <v>1.4405848774602487E-3</v>
+      </c>
+      <c r="AJ34" s="189"/>
+      <c r="AK34" s="189"/>
+      <c r="AL34" s="189"/>
+      <c r="AM34" s="189"/>
+      <c r="AN34" s="189"/>
+      <c r="AO34" s="189"/>
+      <c r="AP34" s="189"/>
+      <c r="AQ34" s="189"/>
+      <c r="AR34" s="189"/>
+      <c r="AS34" s="189"/>
+      <c r="AT34" s="189"/>
+      <c r="AU34" s="189"/>
+      <c r="AV34" s="189"/>
+      <c r="AW34" s="189"/>
+      <c r="AX34" s="189"/>
+      <c r="AY34" s="189"/>
+      <c r="AZ34" s="189"/>
+      <c r="BA34" s="189"/>
+      <c r="BB34" s="189"/>
+      <c r="BC34" s="189"/>
+    </row>
+    <row r="35" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>452</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>484</v>
+      </c>
+      <c r="E35" s="204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G35" s="205" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="205" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="187" t="s">
+        <v>68</v>
+      </c>
+      <c r="J35" s="1">
+        <v>3</v>
+      </c>
+      <c r="K35" s="1">
+        <v>3</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="188">
+        <v>2</v>
+      </c>
+      <c r="N35" s="188">
+        <f>18*320/1000</f>
+        <v>5.76</v>
+      </c>
+      <c r="O35" s="178">
+        <f t="shared" si="18"/>
+        <v>11.52</v>
+      </c>
+      <c r="P35" s="39">
+        <f t="shared" si="30"/>
+        <v>53.384203269050737</v>
+      </c>
+      <c r="Q35" s="188">
+        <f>51*34.5*14/1000000</f>
+        <v>2.4632999999999999E-2</v>
+      </c>
+      <c r="R35" s="64">
+        <f>+N35/Q35</f>
+        <v>233.83266350018269</v>
+      </c>
+      <c r="S35" s="188">
+        <v>2</v>
+      </c>
+      <c r="T35" s="39">
+        <f t="shared" si="31"/>
+        <v>50.039631355304344</v>
+      </c>
+      <c r="U35" s="44">
+        <f>+Q35*S35</f>
+        <v>4.9265999999999997E-2</v>
+      </c>
+      <c r="V35" s="188">
+        <f>51*34.5/10000</f>
+        <v>0.17595</v>
+      </c>
+      <c r="W35" s="188">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X35" s="186">
+        <v>14.21</v>
+      </c>
+      <c r="Y35" s="67">
+        <f t="shared" si="2"/>
+        <v>1.2382125263898662E-2</v>
+      </c>
+      <c r="Z35" s="46">
+        <f t="shared" si="3"/>
+        <v>0.30218978102189775</v>
+      </c>
+      <c r="AA35" s="188">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB35" s="66">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC35" s="12">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD35" s="13">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE35" s="12">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF35" s="12">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG35" s="14">
+        <f t="shared" si="36"/>
+        <v>2.5665446749284744</v>
+      </c>
+      <c r="AH35" s="15">
+        <f t="shared" si="37"/>
+        <v>0.82899393000189725</v>
+      </c>
+      <c r="AI35" s="67">
+        <f t="shared" si="38"/>
+        <v>2.7295292415036288E-3</v>
+      </c>
+      <c r="AJ35" s="189"/>
+      <c r="AK35" s="189"/>
+      <c r="AL35" s="189"/>
+      <c r="AM35" s="189"/>
+      <c r="AN35" s="189"/>
+      <c r="AO35" s="189"/>
+      <c r="AP35" s="189"/>
+      <c r="AQ35" s="189"/>
+      <c r="AR35" s="189"/>
+      <c r="AS35" s="189"/>
+      <c r="AT35" s="189"/>
+      <c r="AU35" s="189"/>
+      <c r="AV35" s="189"/>
+      <c r="AW35" s="189"/>
+      <c r="AX35" s="189"/>
+      <c r="AY35" s="189"/>
+      <c r="AZ35" s="189"/>
+      <c r="BA35" s="189"/>
+      <c r="BB35" s="189"/>
+      <c r="BC35" s="189"/>
+    </row>
+    <row r="36" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="A36" s="52" t="s">
+        <v>488</v>
+      </c>
+      <c r="B36" s="56" t="s">
+        <v>476</v>
+      </c>
+      <c r="C36" s="56">
+        <v>3</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>480</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="56" t="s">
+        <v>487</v>
+      </c>
+      <c r="G36" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="191" t="s">
+        <v>68</v>
+      </c>
+      <c r="J36" s="56">
+        <v>3</v>
+      </c>
+      <c r="K36" s="56">
+        <v>3</v>
+      </c>
+      <c r="L36" s="56">
+        <v>6</v>
+      </c>
+      <c r="M36" s="192">
+        <v>3</v>
+      </c>
+      <c r="N36" s="192">
+        <f>12*210/1000</f>
+        <v>2.52</v>
+      </c>
+      <c r="O36" s="70">
+        <f t="shared" si="18"/>
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="P36" s="57">
+        <f>+$AO$36*O36/SUM($O$27:$O$36)</f>
+        <v>35.033383395314551</v>
+      </c>
+      <c r="Q36" s="192">
+        <f>19*28.5*14/1000000</f>
+        <v>7.5810000000000001E-3</v>
+      </c>
+      <c r="R36" s="193">
+        <f>+N36/Q36</f>
+        <v>332.409972299169</v>
+      </c>
+      <c r="S36" s="192">
+        <v>3</v>
+      </c>
+      <c r="T36" s="57">
+        <f>+$AO$36*S36/SUM($S$27:$S$36)</f>
+        <v>75.059447032956527</v>
+      </c>
+      <c r="U36" s="58">
+        <f>+Q36*S36</f>
+        <v>2.2742999999999999E-2</v>
+      </c>
+      <c r="V36" s="192">
+        <f>19*28.5/10000</f>
+        <v>5.4149999999999997E-2</v>
+      </c>
+      <c r="W36" s="192">
+        <f t="shared" si="41"/>
+        <v>0.16303000000000001</v>
+      </c>
+      <c r="X36" s="194">
+        <v>14.21</v>
+      </c>
+      <c r="Y36" s="195">
+        <f t="shared" si="2"/>
+        <v>3.810696692470091E-3</v>
+      </c>
+      <c r="Z36" s="74">
+        <f t="shared" si="3"/>
+        <v>0.1395019321597252</v>
+      </c>
+      <c r="AA36" s="192">
+        <v>34.103999999999999</v>
+      </c>
+      <c r="AB36" s="24">
+        <f t="shared" si="32"/>
+        <v>4.7803776683087032E-3</v>
+      </c>
+      <c r="AC36" s="25">
+        <f t="shared" si="33"/>
+        <v>23.600544037076975</v>
+      </c>
+      <c r="AD36" s="26">
+        <f t="shared" si="26"/>
+        <v>5.9660506180990458</v>
+      </c>
+      <c r="AE36" s="25">
+        <f t="shared" si="34"/>
+        <v>29.566594655176022</v>
+      </c>
+      <c r="AF36" s="25">
+        <f t="shared" si="35"/>
+        <v>9.5500100736218556</v>
+      </c>
+      <c r="AG36" s="27">
+        <f t="shared" si="36"/>
+        <v>3.910925218938627</v>
+      </c>
+      <c r="AH36" s="28">
+        <f t="shared" si="37"/>
+        <v>1.2632288457171765</v>
+      </c>
+      <c r="AI36" s="29">
+        <f t="shared" si="38"/>
+        <v>1.7912535647367565E-3</v>
+      </c>
+      <c r="AJ36" s="203">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="AK36" s="202">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="AL36" s="31">
+        <f>718150542*AK36/1448</f>
+        <v>8332.1333602209943</v>
+      </c>
+      <c r="AM36" s="31">
+        <f>+AL36/52</f>
+        <v>160.23333385040374</v>
+      </c>
+      <c r="AN36" s="32">
+        <f>74813*AJ36*0.81</f>
+        <v>1781.5967820000001</v>
+      </c>
+      <c r="AO36" s="33">
+        <f>+AP36*AN36</f>
+        <v>575.455760586</v>
+      </c>
+      <c r="AP36" s="34">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="AQ36" s="35">
+        <f>+AO36/AL36</f>
+        <v>6.9064636355116754E-2</v>
+      </c>
+      <c r="AR36" s="189"/>
+      <c r="AS36" s="189"/>
+      <c r="AT36" s="189"/>
+      <c r="AU36" s="189"/>
+      <c r="AV36" s="189"/>
+      <c r="AW36" s="189"/>
+      <c r="AX36" s="189"/>
+      <c r="AY36" s="189"/>
+      <c r="AZ36" s="189"/>
+      <c r="BA36" s="189"/>
+      <c r="BB36" s="189"/>
+      <c r="BC36" s="189"/>
+    </row>
+    <row r="37" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="C37" s="1"/>
+      <c r="M37" s="189"/>
+      <c r="N37" s="189"/>
+      <c r="O37" s="189"/>
+      <c r="P37" s="189"/>
+      <c r="Q37" s="189"/>
+      <c r="R37" s="189"/>
+      <c r="S37" s="189"/>
+      <c r="T37" s="189"/>
+      <c r="U37" s="189"/>
+      <c r="V37" s="189"/>
+      <c r="W37" s="189"/>
+      <c r="X37" s="189"/>
+      <c r="Y37" s="189"/>
+      <c r="Z37" s="189"/>
+      <c r="AA37" s="189"/>
+      <c r="AB37" s="189"/>
+      <c r="AC37" s="188"/>
+      <c r="AD37" s="189"/>
+      <c r="AE37" s="189"/>
+      <c r="AF37" s="189"/>
+      <c r="AG37" s="189"/>
+      <c r="AH37" s="189"/>
+      <c r="AI37" s="189"/>
+      <c r="AJ37" s="189"/>
+      <c r="AK37" s="189"/>
+      <c r="AL37" s="189"/>
+      <c r="AM37" s="189"/>
+      <c r="AN37" s="189"/>
+      <c r="AO37" s="189"/>
+      <c r="AP37" s="189"/>
+      <c r="AQ37" s="189"/>
+      <c r="AR37" s="189"/>
+      <c r="AS37" s="189"/>
+      <c r="AT37" s="189"/>
+      <c r="AU37" s="189"/>
+      <c r="AV37" s="189"/>
+      <c r="AW37" s="189"/>
+      <c r="AX37" s="189"/>
+      <c r="AY37" s="189"/>
+      <c r="AZ37" s="189"/>
+      <c r="BA37" s="189"/>
+      <c r="BB37" s="189"/>
+      <c r="BC37" s="189"/>
+    </row>
+    <row r="38" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M38" s="189"/>
+      <c r="N38" s="189"/>
+      <c r="O38" s="189"/>
+      <c r="P38" s="189"/>
+      <c r="Q38" s="189"/>
+      <c r="R38" s="189"/>
+      <c r="S38" s="189"/>
+      <c r="T38" s="189"/>
+      <c r="U38" s="189"/>
+      <c r="V38" s="189"/>
+      <c r="W38" s="189"/>
+      <c r="X38" s="189"/>
+      <c r="Y38" s="189"/>
+      <c r="Z38" s="189"/>
+      <c r="AA38" s="189"/>
+      <c r="AB38" s="189"/>
+      <c r="AC38" s="188"/>
+      <c r="AD38" s="189"/>
+      <c r="AE38" s="189"/>
+      <c r="AF38" s="189"/>
+      <c r="AG38" s="189"/>
+      <c r="AH38" s="189"/>
+      <c r="AI38" s="189"/>
+      <c r="AJ38" s="189"/>
+      <c r="AK38" s="189"/>
+      <c r="AL38" s="189"/>
+      <c r="AM38" s="189"/>
+      <c r="AN38" s="189"/>
+      <c r="AO38" s="189"/>
+      <c r="AP38" s="189"/>
+      <c r="AQ38" s="189"/>
+      <c r="AR38" s="189"/>
+      <c r="AS38" s="189"/>
+      <c r="AT38" s="189"/>
+      <c r="AU38" s="189"/>
+      <c r="AV38" s="189"/>
+      <c r="AW38" s="189"/>
+      <c r="AX38" s="189"/>
+      <c r="AY38" s="189"/>
+      <c r="AZ38" s="189"/>
+      <c r="BA38" s="189"/>
+      <c r="BB38" s="189"/>
+      <c r="BC38" s="189"/>
+    </row>
+    <row r="39" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M39" s="189"/>
+      <c r="N39" s="189"/>
+      <c r="O39" s="189"/>
+      <c r="P39" s="189"/>
+      <c r="Q39" s="189"/>
+      <c r="R39" s="189"/>
+      <c r="S39" s="189"/>
+      <c r="T39" s="189"/>
+      <c r="U39" s="189"/>
+      <c r="V39" s="189"/>
+      <c r="W39" s="189"/>
+      <c r="X39" s="189"/>
+      <c r="Y39" s="189"/>
+      <c r="Z39" s="189"/>
+      <c r="AA39" s="189"/>
+      <c r="AB39" s="189"/>
+      <c r="AC39" s="188"/>
+      <c r="AD39" s="189"/>
+      <c r="AE39" s="189"/>
+      <c r="AF39" s="189"/>
+      <c r="AG39" s="189"/>
+      <c r="AH39" s="189"/>
+      <c r="AI39" s="189"/>
+      <c r="AJ39" s="189"/>
+      <c r="AK39" s="189"/>
+      <c r="AL39" s="189"/>
+      <c r="AM39" s="189"/>
+      <c r="AN39" s="189"/>
+      <c r="AO39" s="189"/>
+      <c r="AP39" s="189"/>
+      <c r="AQ39" s="189"/>
+      <c r="AR39" s="189"/>
+      <c r="AS39" s="189"/>
+      <c r="AT39" s="189"/>
+      <c r="AU39" s="189"/>
+      <c r="AV39" s="189"/>
+      <c r="AW39" s="189"/>
+      <c r="AX39" s="189"/>
+      <c r="AY39" s="189"/>
+      <c r="AZ39" s="189"/>
+      <c r="BA39" s="189"/>
+      <c r="BB39" s="189"/>
+      <c r="BC39" s="189"/>
+    </row>
+    <row r="40" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M40" s="189"/>
+      <c r="N40" s="189"/>
+      <c r="O40" s="189"/>
+      <c r="P40" s="189"/>
+      <c r="Q40" s="189"/>
+      <c r="R40" s="189"/>
+      <c r="S40" s="189"/>
+      <c r="T40" s="189"/>
+      <c r="U40" s="189"/>
+      <c r="V40" s="189"/>
+      <c r="W40" s="189"/>
+      <c r="X40" s="189"/>
+      <c r="Y40" s="189"/>
+      <c r="Z40" s="189"/>
+      <c r="AA40" s="189"/>
+      <c r="AB40" s="189"/>
+      <c r="AC40" s="188"/>
+      <c r="AD40" s="189"/>
+      <c r="AE40" s="189"/>
+      <c r="AF40" s="189"/>
+      <c r="AG40" s="189"/>
+      <c r="AH40" s="189"/>
+      <c r="AI40" s="189"/>
+      <c r="AJ40" s="189"/>
+      <c r="AK40" s="189"/>
+      <c r="AL40" s="189"/>
+      <c r="AM40" s="189"/>
+      <c r="AN40" s="189"/>
+      <c r="AO40" s="189"/>
+      <c r="AP40" s="189"/>
+      <c r="AQ40" s="189"/>
+      <c r="AR40" s="189"/>
+      <c r="AS40" s="189"/>
+      <c r="AT40" s="189"/>
+      <c r="AU40" s="189"/>
+      <c r="AV40" s="189"/>
+      <c r="AW40" s="189"/>
+      <c r="AX40" s="189"/>
+      <c r="AY40" s="189"/>
+      <c r="AZ40" s="189"/>
+      <c r="BA40" s="189"/>
+      <c r="BB40" s="189"/>
+      <c r="BC40" s="189"/>
+    </row>
+    <row r="41" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M41" s="189"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="189"/>
+      <c r="P41" s="189"/>
+      <c r="Q41" s="189"/>
+      <c r="R41" s="189"/>
+      <c r="S41" s="189"/>
+      <c r="T41" s="189"/>
+      <c r="U41" s="189"/>
+      <c r="V41" s="189"/>
+      <c r="W41" s="189"/>
+      <c r="X41" s="189"/>
+      <c r="Y41" s="189"/>
+      <c r="Z41" s="189"/>
+      <c r="AA41" s="189"/>
+      <c r="AB41" s="189"/>
+      <c r="AC41" s="188"/>
+      <c r="AD41" s="189"/>
+      <c r="AE41" s="189"/>
+      <c r="AF41" s="189"/>
+      <c r="AG41" s="189"/>
+      <c r="AH41" s="189"/>
+      <c r="AI41" s="189"/>
+      <c r="AJ41" s="189"/>
+      <c r="AK41" s="189"/>
+      <c r="AL41" s="189"/>
+      <c r="AM41" s="189"/>
+      <c r="AN41" s="189"/>
+      <c r="AO41" s="189"/>
+      <c r="AP41" s="189"/>
+      <c r="AQ41" s="189"/>
+      <c r="AR41" s="189"/>
+      <c r="AS41" s="189"/>
+      <c r="AT41" s="189"/>
+      <c r="AU41" s="189"/>
+      <c r="AV41" s="189"/>
+      <c r="AW41" s="189"/>
+      <c r="AX41" s="189"/>
+      <c r="AY41" s="189"/>
+      <c r="AZ41" s="189"/>
+      <c r="BA41" s="189"/>
+      <c r="BB41" s="189"/>
+      <c r="BC41" s="189"/>
+    </row>
+    <row r="42" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M42" s="189"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="189"/>
+      <c r="Q42" s="189"/>
+      <c r="R42" s="189"/>
+      <c r="S42" s="189"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="189"/>
+      <c r="W42" s="189"/>
+      <c r="X42" s="189"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="189"/>
+      <c r="AA42" s="189"/>
+      <c r="AB42" s="189"/>
+      <c r="AC42" s="188"/>
+      <c r="AD42" s="189"/>
+      <c r="AE42" s="189"/>
+      <c r="AF42" s="189"/>
+      <c r="AG42" s="189"/>
+      <c r="AH42" s="189"/>
+      <c r="AI42" s="189"/>
+      <c r="AJ42" s="189"/>
+      <c r="AK42" s="189"/>
+      <c r="AL42" s="189"/>
+      <c r="AM42" s="189"/>
+      <c r="AN42" s="189"/>
+      <c r="AO42" s="189"/>
+      <c r="AP42" s="189"/>
+      <c r="AQ42" s="189"/>
+      <c r="AR42" s="189"/>
+      <c r="AS42" s="189"/>
+      <c r="AT42" s="189"/>
+      <c r="AU42" s="189"/>
+      <c r="AV42" s="189"/>
+      <c r="AW42" s="189"/>
+      <c r="AX42" s="189"/>
+      <c r="AY42" s="189"/>
+      <c r="AZ42" s="189"/>
+      <c r="BA42" s="189"/>
+      <c r="BB42" s="189"/>
+      <c r="BC42" s="189"/>
+    </row>
+    <row r="43" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M43" s="189"/>
+      <c r="N43" s="189"/>
+      <c r="O43" s="189"/>
+      <c r="P43" s="189"/>
+      <c r="Q43" s="189"/>
+      <c r="R43" s="189"/>
+      <c r="S43" s="189"/>
+      <c r="T43" s="189"/>
+      <c r="U43" s="189"/>
+      <c r="V43" s="189"/>
+      <c r="W43" s="189"/>
+      <c r="X43" s="189"/>
+      <c r="Y43" s="189"/>
+      <c r="Z43" s="189"/>
+      <c r="AA43" s="189"/>
+      <c r="AB43" s="189"/>
+      <c r="AC43" s="188"/>
+      <c r="AD43" s="189"/>
+      <c r="AE43" s="189"/>
+      <c r="AF43" s="189"/>
+      <c r="AG43" s="189"/>
+      <c r="AH43" s="189"/>
+      <c r="AI43" s="189"/>
+      <c r="AJ43" s="189"/>
+      <c r="AK43" s="189"/>
+      <c r="AL43" s="189"/>
+      <c r="AM43" s="189"/>
+      <c r="AN43" s="189"/>
+      <c r="AO43" s="189"/>
+      <c r="AP43" s="189"/>
+      <c r="AQ43" s="189"/>
+      <c r="AR43" s="189"/>
+      <c r="AS43" s="189"/>
+      <c r="AT43" s="189"/>
+      <c r="AU43" s="189"/>
+      <c r="AV43" s="189"/>
+      <c r="AW43" s="189"/>
+      <c r="AX43" s="189"/>
+      <c r="AY43" s="189"/>
+      <c r="AZ43" s="189"/>
+      <c r="BA43" s="189"/>
+      <c r="BB43" s="189"/>
+      <c r="BC43" s="189"/>
+    </row>
+    <row r="44" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M44" s="189"/>
+      <c r="N44" s="189"/>
+      <c r="O44" s="189"/>
+      <c r="P44" s="189"/>
+      <c r="Q44" s="189"/>
+      <c r="R44" s="189"/>
+      <c r="S44" s="189"/>
+      <c r="T44" s="189"/>
+      <c r="U44" s="189"/>
+      <c r="V44" s="189"/>
+      <c r="W44" s="189"/>
+      <c r="X44" s="189"/>
+      <c r="Y44" s="189"/>
+      <c r="Z44" s="189"/>
+      <c r="AA44" s="189"/>
+      <c r="AB44" s="189"/>
+      <c r="AC44" s="188"/>
+      <c r="AD44" s="189"/>
+      <c r="AE44" s="189"/>
+      <c r="AF44" s="189"/>
+      <c r="AG44" s="189"/>
+      <c r="AH44" s="189"/>
+      <c r="AI44" s="189"/>
+      <c r="AJ44" s="189"/>
+      <c r="AK44" s="189"/>
+      <c r="AL44" s="189"/>
+      <c r="AM44" s="189"/>
+      <c r="AN44" s="189"/>
+      <c r="AO44" s="189"/>
+      <c r="AP44" s="189"/>
+      <c r="AQ44" s="189"/>
+      <c r="AR44" s="189"/>
+      <c r="AS44" s="189"/>
+      <c r="AT44" s="189"/>
+      <c r="AU44" s="189"/>
+      <c r="AV44" s="189"/>
+      <c r="AW44" s="189"/>
+      <c r="AX44" s="189"/>
+      <c r="AY44" s="189"/>
+      <c r="AZ44" s="189"/>
+      <c r="BA44" s="189"/>
+      <c r="BB44" s="189"/>
+      <c r="BC44" s="189"/>
+    </row>
+    <row r="45" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M45" s="189"/>
+      <c r="N45" s="189"/>
+      <c r="O45" s="189"/>
+      <c r="P45" s="189"/>
+      <c r="Q45" s="189"/>
+      <c r="R45" s="189"/>
+      <c r="S45" s="189"/>
+      <c r="T45" s="189"/>
+      <c r="U45" s="189"/>
+      <c r="V45" s="189"/>
+      <c r="W45" s="189"/>
+      <c r="X45" s="189"/>
+      <c r="Y45" s="189"/>
+      <c r="Z45" s="189"/>
+      <c r="AA45" s="189"/>
+      <c r="AB45" s="189"/>
+      <c r="AC45" s="188"/>
+      <c r="AD45" s="189"/>
+      <c r="AE45" s="189"/>
+      <c r="AF45" s="189"/>
+      <c r="AG45" s="189"/>
+      <c r="AH45" s="189"/>
+      <c r="AI45" s="189"/>
+      <c r="AJ45" s="189"/>
+      <c r="AK45" s="189"/>
+      <c r="AL45" s="189"/>
+      <c r="AM45" s="189"/>
+      <c r="AN45" s="189"/>
+      <c r="AO45" s="189"/>
+      <c r="AP45" s="189"/>
+      <c r="AQ45" s="189"/>
+      <c r="AR45" s="189"/>
+      <c r="AS45" s="189"/>
+      <c r="AT45" s="189"/>
+      <c r="AU45" s="189"/>
+      <c r="AV45" s="189"/>
+      <c r="AW45" s="189"/>
+      <c r="AX45" s="189"/>
+      <c r="AY45" s="189"/>
+      <c r="AZ45" s="189"/>
+      <c r="BA45" s="189"/>
+      <c r="BB45" s="189"/>
+      <c r="BC45" s="189"/>
+    </row>
+    <row r="46" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M46" s="189"/>
+      <c r="N46" s="189"/>
+      <c r="O46" s="189"/>
+      <c r="P46" s="189"/>
+      <c r="Q46" s="189"/>
+      <c r="R46" s="189"/>
+      <c r="S46" s="189"/>
+      <c r="T46" s="189"/>
+      <c r="U46" s="189"/>
+      <c r="V46" s="189"/>
+      <c r="W46" s="189"/>
+      <c r="X46" s="189"/>
+      <c r="Y46" s="189"/>
+      <c r="Z46" s="189"/>
+      <c r="AA46" s="189"/>
+      <c r="AB46" s="189"/>
+      <c r="AC46" s="188"/>
+      <c r="AD46" s="189"/>
+      <c r="AE46" s="189"/>
+      <c r="AF46" s="189"/>
+      <c r="AG46" s="189"/>
+      <c r="AH46" s="189"/>
+      <c r="AI46" s="189"/>
+      <c r="AJ46" s="189"/>
+      <c r="AK46" s="189"/>
+      <c r="AL46" s="189"/>
+      <c r="AM46" s="189"/>
+      <c r="AN46" s="189"/>
+      <c r="AO46" s="189"/>
+      <c r="AP46" s="189"/>
+      <c r="AQ46" s="189"/>
+      <c r="AR46" s="189"/>
+      <c r="AS46" s="189"/>
+      <c r="AT46" s="189"/>
+      <c r="AU46" s="189"/>
+      <c r="AV46" s="189"/>
+      <c r="AW46" s="189"/>
+      <c r="AX46" s="189"/>
+      <c r="AY46" s="189"/>
+      <c r="AZ46" s="189"/>
+      <c r="BA46" s="189"/>
+      <c r="BB46" s="189"/>
+      <c r="BC46" s="189"/>
+    </row>
+    <row r="47" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M47" s="189"/>
+      <c r="N47" s="189"/>
+      <c r="O47" s="189"/>
+      <c r="P47" s="189"/>
+      <c r="Q47" s="189"/>
+      <c r="R47" s="189"/>
+      <c r="S47" s="189"/>
+      <c r="T47" s="189"/>
+      <c r="U47" s="189"/>
+      <c r="V47" s="189"/>
+      <c r="W47" s="189"/>
+      <c r="X47" s="189"/>
+      <c r="Y47" s="189"/>
+      <c r="Z47" s="189"/>
+      <c r="AA47" s="189"/>
+      <c r="AB47" s="189"/>
+      <c r="AC47" s="188"/>
+      <c r="AD47" s="189"/>
+      <c r="AE47" s="189"/>
+      <c r="AF47" s="189"/>
+      <c r="AG47" s="189"/>
+      <c r="AH47" s="189"/>
+      <c r="AI47" s="189"/>
+      <c r="AJ47" s="189"/>
+      <c r="AK47" s="189"/>
+      <c r="AL47" s="189"/>
+      <c r="AM47" s="189"/>
+      <c r="AN47" s="189"/>
+      <c r="AO47" s="189"/>
+      <c r="AP47" s="189"/>
+      <c r="AQ47" s="189"/>
+      <c r="AR47" s="189"/>
+      <c r="AS47" s="189"/>
+      <c r="AT47" s="189"/>
+      <c r="AU47" s="189"/>
+      <c r="AV47" s="189"/>
+      <c r="AW47" s="189"/>
+      <c r="AX47" s="189"/>
+      <c r="AY47" s="189"/>
+      <c r="AZ47" s="189"/>
+      <c r="BA47" s="189"/>
+      <c r="BB47" s="189"/>
+      <c r="BC47" s="189"/>
+    </row>
+    <row r="48" spans="1:55" x14ac:dyDescent="0.35">
+      <c r="M48" s="189"/>
+      <c r="N48" s="189"/>
+      <c r="O48" s="189"/>
+      <c r="P48" s="189"/>
+      <c r="Q48" s="189"/>
+      <c r="R48" s="189"/>
+      <c r="S48" s="189"/>
+      <c r="T48" s="189"/>
+      <c r="U48" s="189"/>
+      <c r="V48" s="189"/>
+      <c r="W48" s="189"/>
+      <c r="X48" s="189"/>
+      <c r="Y48" s="189"/>
+      <c r="Z48" s="189"/>
+      <c r="AA48" s="189"/>
+      <c r="AB48" s="189"/>
+      <c r="AC48" s="188"/>
+      <c r="AD48" s="189"/>
+      <c r="AE48" s="189"/>
+      <c r="AF48" s="189"/>
+      <c r="AG48" s="189"/>
+      <c r="AH48" s="189"/>
+      <c r="AI48" s="189"/>
+      <c r="AJ48" s="189"/>
+      <c r="AK48" s="189"/>
+      <c r="AL48" s="189"/>
+      <c r="AM48" s="189"/>
+      <c r="AN48" s="189"/>
+      <c r="AO48" s="189"/>
+      <c r="AP48" s="189"/>
+      <c r="AQ48" s="189"/>
+      <c r="AR48" s="189"/>
+      <c r="AS48" s="189"/>
+      <c r="AT48" s="189"/>
+      <c r="AU48" s="189"/>
+      <c r="AV48" s="189"/>
+      <c r="AW48" s="189"/>
+      <c r="AX48" s="189"/>
+      <c r="AY48" s="189"/>
+      <c r="AZ48" s="189"/>
+      <c r="BA48" s="189"/>
+      <c r="BB48" s="189"/>
+      <c r="BC48" s="189"/>
+    </row>
+    <row r="49" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M49" s="189"/>
+      <c r="N49" s="189"/>
+      <c r="O49" s="189"/>
+      <c r="P49" s="189"/>
+      <c r="Q49" s="189"/>
+      <c r="R49" s="189"/>
+      <c r="S49" s="189"/>
+      <c r="T49" s="189"/>
+      <c r="U49" s="189"/>
+      <c r="V49" s="189"/>
+      <c r="W49" s="189"/>
+      <c r="X49" s="189"/>
+      <c r="Y49" s="189"/>
+      <c r="Z49" s="189"/>
+      <c r="AA49" s="189"/>
+      <c r="AB49" s="189"/>
+      <c r="AC49" s="188"/>
+      <c r="AD49" s="189"/>
+      <c r="AE49" s="189"/>
+      <c r="AF49" s="189"/>
+      <c r="AG49" s="189"/>
+      <c r="AH49" s="189"/>
+      <c r="AI49" s="189"/>
+      <c r="AJ49" s="189"/>
+      <c r="AK49" s="189"/>
+      <c r="AL49" s="189"/>
+      <c r="AM49" s="189"/>
+      <c r="AN49" s="189"/>
+      <c r="AO49" s="189"/>
+      <c r="AP49" s="189"/>
+      <c r="AQ49" s="189"/>
+      <c r="AR49" s="189"/>
+      <c r="AS49" s="189"/>
+      <c r="AT49" s="189"/>
+      <c r="AU49" s="189"/>
+      <c r="AV49" s="189"/>
+      <c r="AW49" s="189"/>
+      <c r="AX49" s="189"/>
+      <c r="AY49" s="189"/>
+      <c r="AZ49" s="189"/>
+      <c r="BA49" s="189"/>
+      <c r="BB49" s="189"/>
+      <c r="BC49" s="189"/>
+    </row>
+    <row r="50" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M50" s="189"/>
+      <c r="N50" s="189"/>
+      <c r="O50" s="189"/>
+      <c r="P50" s="189"/>
+      <c r="Q50" s="189"/>
+      <c r="R50" s="189"/>
+      <c r="S50" s="189"/>
+      <c r="T50" s="189"/>
+      <c r="U50" s="189"/>
+      <c r="V50" s="189"/>
+      <c r="W50" s="189"/>
+      <c r="X50" s="189"/>
+      <c r="Y50" s="189"/>
+      <c r="Z50" s="189"/>
+      <c r="AA50" s="189"/>
+      <c r="AB50" s="189"/>
+      <c r="AC50" s="188"/>
+      <c r="AD50" s="189"/>
+      <c r="AE50" s="189"/>
+      <c r="AF50" s="189"/>
+      <c r="AG50" s="189"/>
+      <c r="AH50" s="189"/>
+      <c r="AI50" s="189"/>
+      <c r="AJ50" s="189"/>
+      <c r="AK50" s="189"/>
+      <c r="AL50" s="189"/>
+      <c r="AM50" s="189"/>
+      <c r="AN50" s="189"/>
+      <c r="AO50" s="189"/>
+      <c r="AP50" s="189"/>
+      <c r="AQ50" s="189"/>
+      <c r="AR50" s="189"/>
+      <c r="AS50" s="189"/>
+      <c r="AT50" s="189"/>
+      <c r="AU50" s="189"/>
+      <c r="AV50" s="189"/>
+      <c r="AW50" s="189"/>
+      <c r="AX50" s="189"/>
+      <c r="AY50" s="189"/>
+      <c r="AZ50" s="189"/>
+      <c r="BA50" s="189"/>
+      <c r="BB50" s="189"/>
+      <c r="BC50" s="189"/>
+    </row>
+    <row r="51" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M51" s="189"/>
+      <c r="N51" s="189"/>
+      <c r="O51" s="189"/>
+      <c r="P51" s="189"/>
+      <c r="Q51" s="189"/>
+      <c r="R51" s="189"/>
+      <c r="S51" s="189"/>
+      <c r="T51" s="189"/>
+      <c r="U51" s="189"/>
+      <c r="V51" s="189"/>
+      <c r="W51" s="189"/>
+      <c r="X51" s="189"/>
+      <c r="Y51" s="189"/>
+      <c r="Z51" s="189"/>
+      <c r="AA51" s="189"/>
+      <c r="AB51" s="189"/>
+      <c r="AC51" s="188"/>
+      <c r="AD51" s="189"/>
+      <c r="AE51" s="189"/>
+      <c r="AF51" s="189"/>
+      <c r="AG51" s="189"/>
+      <c r="AH51" s="189"/>
+      <c r="AI51" s="189"/>
+      <c r="AJ51" s="189"/>
+      <c r="AK51" s="189"/>
+      <c r="AL51" s="189"/>
+      <c r="AM51" s="189"/>
+      <c r="AN51" s="189"/>
+      <c r="AO51" s="189"/>
+      <c r="AP51" s="189"/>
+      <c r="AQ51" s="189"/>
+      <c r="AR51" s="189"/>
+      <c r="AS51" s="189"/>
+      <c r="AT51" s="189"/>
+      <c r="AU51" s="189"/>
+      <c r="AV51" s="189"/>
+      <c r="AW51" s="189"/>
+      <c r="AX51" s="189"/>
+      <c r="AY51" s="189"/>
+      <c r="AZ51" s="189"/>
+      <c r="BA51" s="189"/>
+      <c r="BB51" s="189"/>
+      <c r="BC51" s="189"/>
+    </row>
+    <row r="52" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M52" s="189"/>
+      <c r="N52" s="189"/>
+      <c r="O52" s="189"/>
+      <c r="P52" s="189"/>
+      <c r="Q52" s="189"/>
+      <c r="R52" s="189"/>
+      <c r="S52" s="189"/>
+      <c r="T52" s="189"/>
+      <c r="U52" s="189"/>
+      <c r="V52" s="189"/>
+      <c r="W52" s="189"/>
+      <c r="X52" s="189"/>
+      <c r="Y52" s="189"/>
+      <c r="Z52" s="189"/>
+      <c r="AA52" s="189"/>
+      <c r="AB52" s="189"/>
+      <c r="AC52" s="188"/>
+      <c r="AD52" s="189"/>
+      <c r="AE52" s="189"/>
+      <c r="AF52" s="189"/>
+      <c r="AG52" s="189"/>
+      <c r="AH52" s="189"/>
+      <c r="AI52" s="189"/>
+      <c r="AJ52" s="189"/>
+      <c r="AK52" s="189"/>
+      <c r="AL52" s="189"/>
+      <c r="AM52" s="189"/>
+      <c r="AN52" s="189"/>
+      <c r="AO52" s="189"/>
+      <c r="AP52" s="189"/>
+      <c r="AQ52" s="189"/>
+      <c r="AR52" s="189"/>
+      <c r="AS52" s="189"/>
+      <c r="AT52" s="189"/>
+      <c r="AU52" s="189"/>
+      <c r="AV52" s="189"/>
+      <c r="AW52" s="189"/>
+      <c r="AX52" s="189"/>
+      <c r="AY52" s="189"/>
+      <c r="AZ52" s="189"/>
+      <c r="BA52" s="189"/>
+      <c r="BB52" s="189"/>
+      <c r="BC52" s="189"/>
+    </row>
+    <row r="53" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M53" s="189"/>
+      <c r="N53" s="189"/>
+      <c r="O53" s="189"/>
+      <c r="P53" s="189"/>
+      <c r="Q53" s="189"/>
+      <c r="R53" s="189"/>
+      <c r="S53" s="189"/>
+      <c r="T53" s="189"/>
+      <c r="U53" s="189"/>
+      <c r="V53" s="189"/>
+      <c r="W53" s="189"/>
+      <c r="X53" s="189"/>
+      <c r="Y53" s="189"/>
+      <c r="Z53" s="189"/>
+      <c r="AA53" s="189"/>
+      <c r="AB53" s="189"/>
+      <c r="AC53" s="188"/>
+      <c r="AD53" s="189"/>
+      <c r="AE53" s="189"/>
+      <c r="AF53" s="189"/>
+      <c r="AG53" s="189"/>
+      <c r="AH53" s="189"/>
+      <c r="AI53" s="189"/>
+      <c r="AJ53" s="189"/>
+      <c r="AK53" s="189"/>
+      <c r="AL53" s="189"/>
+      <c r="AM53" s="189"/>
+      <c r="AN53" s="189"/>
+      <c r="AO53" s="189"/>
+      <c r="AP53" s="189"/>
+      <c r="AQ53" s="189"/>
+      <c r="AR53" s="189"/>
+      <c r="AS53" s="189"/>
+      <c r="AT53" s="189"/>
+      <c r="AU53" s="189"/>
+      <c r="AV53" s="189"/>
+      <c r="AW53" s="189"/>
+      <c r="AX53" s="189"/>
+      <c r="AY53" s="189"/>
+      <c r="AZ53" s="189"/>
+      <c r="BA53" s="189"/>
+      <c r="BB53" s="189"/>
+      <c r="BC53" s="189"/>
+    </row>
+    <row r="54" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M54" s="189"/>
+      <c r="N54" s="189"/>
+      <c r="O54" s="189"/>
+      <c r="P54" s="189"/>
+      <c r="Q54" s="189"/>
+      <c r="R54" s="189"/>
+      <c r="S54" s="189"/>
+      <c r="T54" s="189"/>
+      <c r="U54" s="189"/>
+      <c r="V54" s="189"/>
+      <c r="W54" s="189"/>
+      <c r="X54" s="189"/>
+      <c r="Y54" s="189"/>
+      <c r="Z54" s="189"/>
+      <c r="AA54" s="189"/>
+      <c r="AB54" s="189"/>
+      <c r="AC54" s="188"/>
+      <c r="AD54" s="189"/>
+      <c r="AE54" s="189"/>
+      <c r="AF54" s="189"/>
+      <c r="AG54" s="189"/>
+      <c r="AH54" s="189"/>
+      <c r="AI54" s="189"/>
+      <c r="AJ54" s="189"/>
+      <c r="AK54" s="189"/>
+      <c r="AL54" s="189"/>
+      <c r="AM54" s="189"/>
+      <c r="AN54" s="189"/>
+      <c r="AO54" s="189"/>
+      <c r="AP54" s="189"/>
+      <c r="AQ54" s="189"/>
+      <c r="AR54" s="189"/>
+      <c r="AS54" s="189"/>
+      <c r="AT54" s="189"/>
+      <c r="AU54" s="189"/>
+      <c r="AV54" s="189"/>
+      <c r="AW54" s="189"/>
+      <c r="AX54" s="189"/>
+      <c r="AY54" s="189"/>
+      <c r="AZ54" s="189"/>
+      <c r="BA54" s="189"/>
+      <c r="BB54" s="189"/>
+      <c r="BC54" s="189"/>
+    </row>
+    <row r="55" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M55" s="189"/>
+      <c r="N55" s="189"/>
+      <c r="O55" s="189"/>
+      <c r="P55" s="189"/>
+      <c r="Q55" s="189"/>
+      <c r="R55" s="189"/>
+      <c r="S55" s="189"/>
+      <c r="T55" s="189"/>
+      <c r="U55" s="189"/>
+      <c r="V55" s="189"/>
+      <c r="W55" s="189"/>
+      <c r="X55" s="189"/>
+      <c r="Y55" s="189"/>
+      <c r="Z55" s="189"/>
+      <c r="AA55" s="189"/>
+      <c r="AB55" s="189"/>
+      <c r="AC55" s="188"/>
+      <c r="AD55" s="189"/>
+      <c r="AE55" s="189"/>
+      <c r="AF55" s="189"/>
+      <c r="AG55" s="189"/>
+      <c r="AH55" s="189"/>
+      <c r="AI55" s="189"/>
+      <c r="AJ55" s="189"/>
+      <c r="AK55" s="189"/>
+      <c r="AL55" s="189"/>
+      <c r="AM55" s="189"/>
+      <c r="AN55" s="189"/>
+      <c r="AO55" s="189"/>
+      <c r="AP55" s="189"/>
+      <c r="AQ55" s="189"/>
+      <c r="AR55" s="189"/>
+      <c r="AS55" s="189"/>
+      <c r="AT55" s="189"/>
+      <c r="AU55" s="189"/>
+      <c r="AV55" s="189"/>
+      <c r="AW55" s="189"/>
+      <c r="AX55" s="189"/>
+      <c r="AY55" s="189"/>
+      <c r="AZ55" s="189"/>
+      <c r="BA55" s="189"/>
+      <c r="BB55" s="189"/>
+      <c r="BC55" s="189"/>
+    </row>
+    <row r="56" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M56" s="189"/>
+      <c r="N56" s="189"/>
+      <c r="O56" s="189"/>
+      <c r="P56" s="189"/>
+      <c r="Q56" s="189"/>
+      <c r="R56" s="189"/>
+      <c r="S56" s="189"/>
+      <c r="T56" s="189"/>
+      <c r="U56" s="189"/>
+      <c r="V56" s="189"/>
+      <c r="W56" s="189"/>
+      <c r="X56" s="189"/>
+      <c r="Y56" s="189"/>
+      <c r="Z56" s="189"/>
+      <c r="AA56" s="189"/>
+      <c r="AB56" s="189"/>
+      <c r="AC56" s="188"/>
+      <c r="AD56" s="189"/>
+      <c r="AE56" s="189"/>
+      <c r="AF56" s="189"/>
+      <c r="AG56" s="189"/>
+      <c r="AH56" s="189"/>
+      <c r="AI56" s="189"/>
+      <c r="AJ56" s="189"/>
+      <c r="AK56" s="189"/>
+      <c r="AL56" s="189"/>
+      <c r="AM56" s="189"/>
+      <c r="AN56" s="189"/>
+      <c r="AO56" s="189"/>
+      <c r="AP56" s="189"/>
+      <c r="AQ56" s="189"/>
+      <c r="AR56" s="189"/>
+      <c r="AS56" s="189"/>
+      <c r="AT56" s="189"/>
+      <c r="AU56" s="189"/>
+      <c r="AV56" s="189"/>
+      <c r="AW56" s="189"/>
+      <c r="AX56" s="189"/>
+      <c r="AY56" s="189"/>
+      <c r="AZ56" s="189"/>
+      <c r="BA56" s="189"/>
+      <c r="BB56" s="189"/>
+      <c r="BC56" s="189"/>
+    </row>
+    <row r="57" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M57" s="189"/>
+      <c r="N57" s="189"/>
+      <c r="O57" s="189"/>
+      <c r="P57" s="189"/>
+      <c r="Q57" s="189"/>
+      <c r="R57" s="189"/>
+      <c r="S57" s="189"/>
+      <c r="T57" s="189"/>
+      <c r="U57" s="189"/>
+      <c r="V57" s="189"/>
+      <c r="W57" s="189"/>
+      <c r="X57" s="189"/>
+      <c r="Y57" s="189"/>
+      <c r="Z57" s="189"/>
+      <c r="AA57" s="189"/>
+      <c r="AB57" s="189"/>
+      <c r="AC57" s="188"/>
+      <c r="AD57" s="189"/>
+      <c r="AE57" s="189"/>
+      <c r="AF57" s="189"/>
+      <c r="AG57" s="189"/>
+      <c r="AH57" s="189"/>
+      <c r="AI57" s="189"/>
+      <c r="AJ57" s="189"/>
+      <c r="AK57" s="189"/>
+      <c r="AL57" s="189"/>
+      <c r="AM57" s="189"/>
+      <c r="AN57" s="189"/>
+      <c r="AO57" s="189"/>
+      <c r="AP57" s="189"/>
+      <c r="AQ57" s="189"/>
+      <c r="AR57" s="189"/>
+      <c r="AS57" s="189"/>
+      <c r="AT57" s="189"/>
+      <c r="AU57" s="189"/>
+      <c r="AV57" s="189"/>
+      <c r="AW57" s="189"/>
+      <c r="AX57" s="189"/>
+      <c r="AY57" s="189"/>
+      <c r="AZ57" s="189"/>
+      <c r="BA57" s="189"/>
+      <c r="BB57" s="189"/>
+      <c r="BC57" s="189"/>
+    </row>
+    <row r="58" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M58" s="189"/>
+      <c r="N58" s="189"/>
+      <c r="O58" s="189"/>
+      <c r="P58" s="189"/>
+      <c r="Q58" s="189"/>
+      <c r="R58" s="189"/>
+      <c r="S58" s="189"/>
+      <c r="T58" s="189"/>
+      <c r="U58" s="189"/>
+      <c r="V58" s="189"/>
+      <c r="W58" s="189"/>
+      <c r="X58" s="189"/>
+      <c r="Y58" s="189"/>
+      <c r="Z58" s="189"/>
+      <c r="AA58" s="189"/>
+      <c r="AB58" s="189"/>
+      <c r="AC58" s="188"/>
+      <c r="AD58" s="189"/>
+      <c r="AE58" s="189"/>
+      <c r="AF58" s="189"/>
+      <c r="AG58" s="189"/>
+      <c r="AH58" s="189"/>
+      <c r="AI58" s="189"/>
+      <c r="AJ58" s="189"/>
+      <c r="AK58" s="189"/>
+      <c r="AL58" s="189"/>
+      <c r="AM58" s="189"/>
+      <c r="AN58" s="189"/>
+      <c r="AO58" s="189"/>
+      <c r="AP58" s="189"/>
+      <c r="AQ58" s="189"/>
+      <c r="AR58" s="189"/>
+      <c r="AS58" s="189"/>
+      <c r="AT58" s="189"/>
+      <c r="AU58" s="189"/>
+      <c r="AV58" s="189"/>
+      <c r="AW58" s="189"/>
+      <c r="AX58" s="189"/>
+      <c r="AY58" s="189"/>
+      <c r="AZ58" s="189"/>
+      <c r="BA58" s="189"/>
+      <c r="BB58" s="189"/>
+      <c r="BC58" s="189"/>
+    </row>
+    <row r="59" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M59" s="189"/>
+      <c r="N59" s="189"/>
+      <c r="O59" s="189"/>
+      <c r="P59" s="189"/>
+      <c r="Q59" s="189"/>
+      <c r="R59" s="189"/>
+      <c r="S59" s="189"/>
+      <c r="T59" s="189"/>
+      <c r="U59" s="189"/>
+      <c r="V59" s="189"/>
+      <c r="W59" s="189"/>
+      <c r="X59" s="189"/>
+      <c r="Y59" s="189"/>
+      <c r="Z59" s="189"/>
+      <c r="AA59" s="189"/>
+      <c r="AB59" s="189"/>
+      <c r="AC59" s="188"/>
+      <c r="AD59" s="189"/>
+      <c r="AE59" s="189"/>
+      <c r="AF59" s="189"/>
+      <c r="AG59" s="189"/>
+      <c r="AH59" s="189"/>
+      <c r="AI59" s="189"/>
+      <c r="AJ59" s="189"/>
+      <c r="AK59" s="189"/>
+      <c r="AL59" s="189"/>
+      <c r="AM59" s="189"/>
+      <c r="AN59" s="189"/>
+      <c r="AO59" s="189"/>
+      <c r="AP59" s="189"/>
+      <c r="AQ59" s="189"/>
+      <c r="AR59" s="189"/>
+      <c r="AS59" s="189"/>
+      <c r="AT59" s="189"/>
+      <c r="AU59" s="189"/>
+      <c r="AV59" s="189"/>
+      <c r="AW59" s="189"/>
+      <c r="AX59" s="189"/>
+      <c r="AY59" s="189"/>
+      <c r="AZ59" s="189"/>
+      <c r="BA59" s="189"/>
+      <c r="BB59" s="189"/>
+      <c r="BC59" s="189"/>
+    </row>
+    <row r="60" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M60" s="189"/>
+      <c r="N60" s="189"/>
+      <c r="O60" s="189"/>
+      <c r="P60" s="189"/>
+      <c r="Q60" s="189"/>
+      <c r="R60" s="189"/>
+      <c r="S60" s="189"/>
+      <c r="T60" s="189"/>
+      <c r="U60" s="189"/>
+      <c r="V60" s="189"/>
+      <c r="W60" s="189"/>
+      <c r="X60" s="189"/>
+      <c r="Y60" s="189"/>
+      <c r="Z60" s="189"/>
+      <c r="AA60" s="189"/>
+      <c r="AB60" s="189"/>
+      <c r="AC60" s="188"/>
+      <c r="AD60" s="189"/>
+      <c r="AE60" s="189"/>
+      <c r="AF60" s="189"/>
+      <c r="AG60" s="189"/>
+      <c r="AH60" s="189"/>
+      <c r="AI60" s="189"/>
+      <c r="AJ60" s="189"/>
+      <c r="AK60" s="189"/>
+      <c r="AL60" s="189"/>
+      <c r="AM60" s="189"/>
+      <c r="AN60" s="189"/>
+      <c r="AO60" s="189"/>
+      <c r="AP60" s="189"/>
+      <c r="AQ60" s="189"/>
+      <c r="AR60" s="189"/>
+      <c r="AS60" s="189"/>
+      <c r="AT60" s="189"/>
+      <c r="AU60" s="189"/>
+      <c r="AV60" s="189"/>
+      <c r="AW60" s="189"/>
+      <c r="AX60" s="189"/>
+      <c r="AY60" s="189"/>
+      <c r="AZ60" s="189"/>
+      <c r="BA60" s="189"/>
+      <c r="BB60" s="189"/>
+      <c r="BC60" s="189"/>
+    </row>
+    <row r="61" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M61" s="189"/>
+      <c r="N61" s="189"/>
+      <c r="O61" s="189"/>
+      <c r="P61" s="189"/>
+      <c r="Q61" s="189"/>
+      <c r="R61" s="189"/>
+      <c r="S61" s="189"/>
+      <c r="T61" s="189"/>
+      <c r="U61" s="189"/>
+      <c r="V61" s="189"/>
+      <c r="W61" s="189"/>
+      <c r="X61" s="189"/>
+      <c r="Y61" s="189"/>
+      <c r="Z61" s="189"/>
+      <c r="AA61" s="189"/>
+      <c r="AB61" s="189"/>
+      <c r="AC61" s="188"/>
+      <c r="AD61" s="189"/>
+      <c r="AE61" s="189"/>
+      <c r="AF61" s="189"/>
+      <c r="AG61" s="189"/>
+      <c r="AH61" s="189"/>
+      <c r="AI61" s="189"/>
+      <c r="AJ61" s="189"/>
+      <c r="AK61" s="189"/>
+      <c r="AL61" s="189"/>
+      <c r="AM61" s="189"/>
+      <c r="AN61" s="189"/>
+      <c r="AO61" s="189"/>
+      <c r="AP61" s="189"/>
+      <c r="AQ61" s="189"/>
+      <c r="AR61" s="189"/>
+      <c r="AS61" s="189"/>
+      <c r="AT61" s="189"/>
+      <c r="AU61" s="189"/>
+      <c r="AV61" s="189"/>
+      <c r="AW61" s="189"/>
+      <c r="AX61" s="189"/>
+      <c r="AY61" s="189"/>
+      <c r="AZ61" s="189"/>
+      <c r="BA61" s="189"/>
+      <c r="BB61" s="189"/>
+      <c r="BC61" s="189"/>
+    </row>
+    <row r="62" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M62" s="189"/>
+      <c r="N62" s="189"/>
+      <c r="O62" s="189"/>
+      <c r="P62" s="189"/>
+      <c r="Q62" s="189"/>
+      <c r="R62" s="189"/>
+      <c r="S62" s="189"/>
+      <c r="T62" s="189"/>
+      <c r="U62" s="189"/>
+      <c r="V62" s="189"/>
+      <c r="W62" s="189"/>
+      <c r="X62" s="189"/>
+      <c r="Y62" s="189"/>
+      <c r="Z62" s="189"/>
+      <c r="AA62" s="189"/>
+      <c r="AB62" s="189"/>
+      <c r="AC62" s="188"/>
+      <c r="AD62" s="189"/>
+      <c r="AE62" s="189"/>
+      <c r="AF62" s="189"/>
+      <c r="AG62" s="189"/>
+      <c r="AH62" s="189"/>
+      <c r="AI62" s="189"/>
+      <c r="AJ62" s="189"/>
+      <c r="AK62" s="189"/>
+      <c r="AL62" s="189"/>
+      <c r="AM62" s="189"/>
+      <c r="AN62" s="189"/>
+      <c r="AO62" s="189"/>
+      <c r="AP62" s="189"/>
+      <c r="AQ62" s="189"/>
+      <c r="AR62" s="189"/>
+      <c r="AS62" s="189"/>
+      <c r="AT62" s="189"/>
+      <c r="AU62" s="189"/>
+      <c r="AV62" s="189"/>
+      <c r="AW62" s="189"/>
+      <c r="AX62" s="189"/>
+      <c r="AY62" s="189"/>
+      <c r="AZ62" s="189"/>
+      <c r="BA62" s="189"/>
+      <c r="BB62" s="189"/>
+      <c r="BC62" s="189"/>
+    </row>
+    <row r="63" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M63" s="189"/>
+      <c r="N63" s="189"/>
+      <c r="O63" s="189"/>
+      <c r="P63" s="189"/>
+      <c r="Q63" s="189"/>
+      <c r="R63" s="189"/>
+      <c r="S63" s="189"/>
+      <c r="T63" s="189"/>
+      <c r="U63" s="189"/>
+      <c r="V63" s="189"/>
+      <c r="W63" s="189"/>
+      <c r="X63" s="189"/>
+      <c r="Y63" s="189"/>
+      <c r="Z63" s="189"/>
+      <c r="AA63" s="189"/>
+      <c r="AB63" s="189"/>
+      <c r="AC63" s="188"/>
+      <c r="AD63" s="189"/>
+      <c r="AE63" s="189"/>
+      <c r="AF63" s="189"/>
+      <c r="AG63" s="189"/>
+      <c r="AH63" s="189"/>
+      <c r="AI63" s="189"/>
+      <c r="AJ63" s="189"/>
+      <c r="AK63" s="189"/>
+      <c r="AL63" s="189"/>
+      <c r="AM63" s="189"/>
+      <c r="AN63" s="189"/>
+      <c r="AO63" s="189"/>
+      <c r="AP63" s="189"/>
+      <c r="AQ63" s="189"/>
+      <c r="AR63" s="189"/>
+      <c r="AS63" s="189"/>
+      <c r="AT63" s="189"/>
+      <c r="AU63" s="189"/>
+      <c r="AV63" s="189"/>
+      <c r="AW63" s="189"/>
+      <c r="AX63" s="189"/>
+      <c r="AY63" s="189"/>
+      <c r="AZ63" s="189"/>
+      <c r="BA63" s="189"/>
+      <c r="BB63" s="189"/>
+      <c r="BC63" s="189"/>
+    </row>
+    <row r="64" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M64" s="189"/>
+      <c r="N64" s="189"/>
+      <c r="O64" s="189"/>
+      <c r="P64" s="189"/>
+      <c r="Q64" s="189"/>
+      <c r="R64" s="189"/>
+      <c r="S64" s="189"/>
+      <c r="T64" s="189"/>
+      <c r="U64" s="189"/>
+      <c r="V64" s="189"/>
+      <c r="W64" s="189"/>
+      <c r="X64" s="189"/>
+      <c r="Y64" s="189"/>
+      <c r="Z64" s="189"/>
+      <c r="AA64" s="189"/>
+      <c r="AB64" s="189"/>
+      <c r="AC64" s="188"/>
+      <c r="AD64" s="189"/>
+      <c r="AE64" s="189"/>
+      <c r="AF64" s="189"/>
+      <c r="AG64" s="189"/>
+      <c r="AH64" s="189"/>
+      <c r="AI64" s="189"/>
+      <c r="AJ64" s="189"/>
+      <c r="AK64" s="189"/>
+      <c r="AL64" s="189"/>
+      <c r="AM64" s="189"/>
+      <c r="AN64" s="189"/>
+      <c r="AO64" s="189"/>
+      <c r="AP64" s="189"/>
+      <c r="AQ64" s="189"/>
+      <c r="AR64" s="189"/>
+      <c r="AS64" s="189"/>
+      <c r="AT64" s="189"/>
+      <c r="AU64" s="189"/>
+      <c r="AV64" s="189"/>
+      <c r="AW64" s="189"/>
+      <c r="AX64" s="189"/>
+      <c r="AY64" s="189"/>
+      <c r="AZ64" s="189"/>
+      <c r="BA64" s="189"/>
+      <c r="BB64" s="189"/>
+      <c r="BC64" s="189"/>
+    </row>
+    <row r="65" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M65" s="189"/>
+      <c r="N65" s="189"/>
+      <c r="O65" s="189"/>
+      <c r="P65" s="189"/>
+      <c r="Q65" s="189"/>
+      <c r="R65" s="189"/>
+      <c r="S65" s="189"/>
+      <c r="T65" s="189"/>
+      <c r="U65" s="189"/>
+      <c r="V65" s="189"/>
+      <c r="W65" s="189"/>
+      <c r="X65" s="189"/>
+      <c r="Y65" s="189"/>
+      <c r="Z65" s="189"/>
+      <c r="AA65" s="189"/>
+      <c r="AB65" s="189"/>
+      <c r="AC65" s="188"/>
+      <c r="AD65" s="189"/>
+      <c r="AE65" s="189"/>
+      <c r="AF65" s="189"/>
+      <c r="AG65" s="189"/>
+      <c r="AH65" s="189"/>
+      <c r="AI65" s="189"/>
+      <c r="AJ65" s="189"/>
+      <c r="AK65" s="189"/>
+      <c r="AL65" s="189"/>
+      <c r="AM65" s="189"/>
+      <c r="AN65" s="189"/>
+      <c r="AO65" s="189"/>
+      <c r="AP65" s="189"/>
+      <c r="AQ65" s="189"/>
+      <c r="AR65" s="189"/>
+      <c r="AS65" s="189"/>
+      <c r="AT65" s="189"/>
+      <c r="AU65" s="189"/>
+      <c r="AV65" s="189"/>
+      <c r="AW65" s="189"/>
+      <c r="AX65" s="189"/>
+      <c r="AY65" s="189"/>
+      <c r="AZ65" s="189"/>
+      <c r="BA65" s="189"/>
+      <c r="BB65" s="189"/>
+      <c r="BC65" s="189"/>
+    </row>
+    <row r="66" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M66" s="189"/>
+      <c r="N66" s="189"/>
+      <c r="O66" s="189"/>
+      <c r="P66" s="189"/>
+      <c r="Q66" s="189"/>
+      <c r="R66" s="189"/>
+      <c r="S66" s="189"/>
+      <c r="T66" s="189"/>
+      <c r="U66" s="189"/>
+      <c r="V66" s="189"/>
+      <c r="W66" s="189"/>
+      <c r="X66" s="189"/>
+      <c r="Y66" s="189"/>
+      <c r="Z66" s="189"/>
+      <c r="AA66" s="189"/>
+      <c r="AB66" s="189"/>
+      <c r="AC66" s="188"/>
+      <c r="AD66" s="189"/>
+      <c r="AE66" s="189"/>
+      <c r="AF66" s="189"/>
+      <c r="AG66" s="189"/>
+      <c r="AH66" s="189"/>
+      <c r="AI66" s="189"/>
+      <c r="AJ66" s="189"/>
+      <c r="AK66" s="189"/>
+      <c r="AL66" s="189"/>
+      <c r="AM66" s="189"/>
+      <c r="AN66" s="189"/>
+      <c r="AO66" s="189"/>
+      <c r="AP66" s="189"/>
+      <c r="AQ66" s="189"/>
+      <c r="AR66" s="189"/>
+      <c r="AS66" s="189"/>
+      <c r="AT66" s="189"/>
+      <c r="AU66" s="189"/>
+      <c r="AV66" s="189"/>
+      <c r="AW66" s="189"/>
+      <c r="AX66" s="189"/>
+      <c r="AY66" s="189"/>
+      <c r="AZ66" s="189"/>
+      <c r="BA66" s="189"/>
+      <c r="BB66" s="189"/>
+      <c r="BC66" s="189"/>
+    </row>
+    <row r="67" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M67" s="189"/>
+      <c r="N67" s="189"/>
+      <c r="O67" s="189"/>
+      <c r="P67" s="189"/>
+      <c r="Q67" s="189"/>
+      <c r="R67" s="189"/>
+      <c r="S67" s="189"/>
+      <c r="T67" s="189"/>
+      <c r="U67" s="189"/>
+      <c r="V67" s="189"/>
+      <c r="W67" s="189"/>
+      <c r="X67" s="189"/>
+      <c r="Y67" s="189"/>
+      <c r="Z67" s="189"/>
+      <c r="AA67" s="189"/>
+      <c r="AB67" s="189"/>
+      <c r="AC67" s="188"/>
+      <c r="AD67" s="189"/>
+      <c r="AE67" s="189"/>
+      <c r="AF67" s="189"/>
+      <c r="AG67" s="189"/>
+      <c r="AH67" s="189"/>
+      <c r="AI67" s="189"/>
+      <c r="AJ67" s="189"/>
+      <c r="AK67" s="189"/>
+      <c r="AL67" s="189"/>
+      <c r="AM67" s="189"/>
+      <c r="AN67" s="189"/>
+      <c r="AO67" s="189"/>
+      <c r="AP67" s="189"/>
+      <c r="AQ67" s="189"/>
+      <c r="AR67" s="189"/>
+      <c r="AS67" s="189"/>
+      <c r="AT67" s="189"/>
+      <c r="AU67" s="189"/>
+      <c r="AV67" s="189"/>
+      <c r="AW67" s="189"/>
+      <c r="AX67" s="189"/>
+      <c r="AY67" s="189"/>
+      <c r="AZ67" s="189"/>
+      <c r="BA67" s="189"/>
+      <c r="BB67" s="189"/>
+      <c r="BC67" s="189"/>
+    </row>
+    <row r="68" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M68" s="189"/>
+      <c r="N68" s="189"/>
+      <c r="O68" s="189"/>
+      <c r="P68" s="189"/>
+      <c r="Q68" s="189"/>
+      <c r="R68" s="189"/>
+      <c r="S68" s="189"/>
+      <c r="T68" s="189"/>
+      <c r="U68" s="189"/>
+      <c r="V68" s="189"/>
+      <c r="W68" s="189"/>
+      <c r="X68" s="189"/>
+      <c r="Y68" s="189"/>
+      <c r="Z68" s="189"/>
+      <c r="AA68" s="189"/>
+      <c r="AB68" s="189"/>
+      <c r="AC68" s="188"/>
+      <c r="AD68" s="189"/>
+      <c r="AE68" s="189"/>
+      <c r="AF68" s="189"/>
+      <c r="AG68" s="189"/>
+      <c r="AH68" s="189"/>
+      <c r="AI68" s="189"/>
+      <c r="AJ68" s="189"/>
+      <c r="AK68" s="189"/>
+      <c r="AL68" s="189"/>
+      <c r="AM68" s="189"/>
+      <c r="AN68" s="189"/>
+      <c r="AO68" s="189"/>
+      <c r="AP68" s="189"/>
+      <c r="AQ68" s="189"/>
+      <c r="AR68" s="189"/>
+      <c r="AS68" s="189"/>
+      <c r="AT68" s="189"/>
+      <c r="AU68" s="189"/>
+      <c r="AV68" s="189"/>
+      <c r="AW68" s="189"/>
+      <c r="AX68" s="189"/>
+      <c r="AY68" s="189"/>
+      <c r="AZ68" s="189"/>
+      <c r="BA68" s="189"/>
+      <c r="BB68" s="189"/>
+      <c r="BC68" s="189"/>
+    </row>
+    <row r="69" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M69" s="189"/>
+      <c r="N69" s="189"/>
+      <c r="O69" s="189"/>
+      <c r="P69" s="189"/>
+      <c r="Q69" s="189"/>
+      <c r="R69" s="189"/>
+      <c r="S69" s="189"/>
+      <c r="T69" s="189"/>
+      <c r="U69" s="189"/>
+      <c r="V69" s="189"/>
+      <c r="W69" s="189"/>
+      <c r="X69" s="189"/>
+      <c r="Y69" s="189"/>
+      <c r="Z69" s="189"/>
+      <c r="AA69" s="189"/>
+      <c r="AB69" s="189"/>
+      <c r="AC69" s="188"/>
+      <c r="AD69" s="189"/>
+      <c r="AE69" s="189"/>
+      <c r="AF69" s="189"/>
+      <c r="AG69" s="189"/>
+      <c r="AH69" s="189"/>
+      <c r="AI69" s="189"/>
+      <c r="AJ69" s="189"/>
+      <c r="AK69" s="189"/>
+      <c r="AL69" s="189"/>
+      <c r="AM69" s="189"/>
+      <c r="AN69" s="189"/>
+      <c r="AO69" s="189"/>
+      <c r="AP69" s="189"/>
+      <c r="AQ69" s="189"/>
+      <c r="AR69" s="189"/>
+      <c r="AS69" s="189"/>
+      <c r="AT69" s="189"/>
+      <c r="AU69" s="189"/>
+      <c r="AV69" s="189"/>
+      <c r="AW69" s="189"/>
+      <c r="AX69" s="189"/>
+      <c r="AY69" s="189"/>
+      <c r="AZ69" s="189"/>
+      <c r="BA69" s="189"/>
+      <c r="BB69" s="189"/>
+      <c r="BC69" s="189"/>
+    </row>
+    <row r="70" spans="13:55" x14ac:dyDescent="0.35">
+      <c r="M70" s="189"/>
+      <c r="N70" s="189"/>
+      <c r="O70" s="189"/>
+      <c r="P70" s="189"/>
+      <c r="Q70" s="189"/>
+      <c r="R70" s="189"/>
+      <c r="S70" s="189"/>
+      <c r="T70" s="189"/>
+      <c r="U70" s="189"/>
+      <c r="V70" s="189"/>
+      <c r="W70" s="189"/>
+      <c r="X70" s="189"/>
+      <c r="Y70" s="189"/>
+      <c r="Z70" s="189"/>
+      <c r="AA70" s="189"/>
+      <c r="AB70" s="189"/>
+      <c r="AC70" s="188"/>
+      <c r="AD70" s="189"/>
+      <c r="AE70" s="189"/>
+      <c r="AF70" s="189"/>
+      <c r="AG70" s="189"/>
+      <c r="AH70" s="189"/>
+      <c r="AI70" s="189"/>
+      <c r="AJ70" s="189"/>
+      <c r="AK70" s="189"/>
+      <c r="AL70" s="189"/>
+      <c r="AM70" s="189"/>
+      <c r="AN70" s="189"/>
+      <c r="AO70" s="189"/>
+      <c r="AP70" s="189"/>
+      <c r="AQ70" s="189"/>
+      <c r="AR70" s="189"/>
+      <c r="AS70" s="189"/>
+      <c r="AT70" s="189"/>
+      <c r="AU70" s="189"/>
+      <c r="AV70" s="189"/>
+      <c r="AW70" s="189"/>
+      <c r="AX70" s="189"/>
+      <c r="AY70" s="189"/>
+      <c r="AZ70" s="189"/>
+      <c r="BA70" s="189"/>
+      <c r="BB70" s="189"/>
+      <c r="BC70" s="189"/>
     </row>
     <row r="1048576" spans="15:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O1048576">
         <f>SUM(O2:O1048575)</f>
-        <v>4152.7579999999989</v>
+        <v>4220.5080000000007</v>
       </c>
     </row>
   </sheetData>
@@ -10149,63 +13139,63 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="194" t="s">
+      <c r="A4" s="198" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="194"/>
-      <c r="C4" s="194" t="s">
+      <c r="B4" s="198"/>
+      <c r="C4" s="198" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194" t="s">
+      <c r="D4" s="198"/>
+      <c r="E4" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="194"/>
-      <c r="G4" s="194" t="s">
+      <c r="F4" s="198"/>
+      <c r="G4" s="198" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="194"/>
+      <c r="H4" s="198"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="194"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="198"/>
     </row>
     <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="195">
+      <c r="A6" s="199">
         <f>'Propuesta Reubicacion en camara'!D33</f>
         <v>0.74927917763570273</v>
       </c>
-      <c r="B6" s="195"/>
-      <c r="C6" s="196" t="str">
+      <c r="B6" s="199"/>
+      <c r="C6" s="200" t="str">
         <f>"USD "&amp;TEXT(G25,"#,##0")&amp;" - "&amp;TEXT(H25,"#,##0")</f>
         <v>USD 654 - 982</v>
       </c>
-      <c r="D6" s="196"/>
-      <c r="E6" s="197" t="str">
+      <c r="D6" s="200"/>
+      <c r="E6" s="201" t="str">
         <f>"USD "&amp;TEXT(G25/D12,"#,##0")&amp;" - "&amp;TEXT(H25/D12,"#,##0")</f>
         <v>USD 13,087 - 19,630</v>
       </c>
-      <c r="F6" s="197"/>
-      <c r="G6" s="197" t="s">
+      <c r="F6" s="201"/>
+      <c r="G6" s="201" t="s">
         <v>127</v>
       </c>
-      <c r="H6" s="197"/>
+      <c r="H6" s="201"/>
     </row>
     <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="195"/>
-      <c r="B7" s="195"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="197"/>
-      <c r="F7" s="197"/>
-      <c r="G7" s="197"/>
-      <c r="H7" s="197"/>
+      <c r="A7" s="199"/>
+      <c r="B7" s="199"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="201"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="93" t="s">
@@ -10566,36 +13556,36 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="192" t="s">
+      <c r="A32" s="196" t="s">
         <v>316</v>
       </c>
-      <c r="B32" s="192"/>
-      <c r="C32" s="192"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="192"/>
-      <c r="G32" s="192"/>
-      <c r="H32" s="192"/>
+      <c r="B32" s="196"/>
+      <c r="C32" s="196"/>
+      <c r="D32" s="196"/>
+      <c r="E32" s="196"/>
+      <c r="F32" s="196"/>
+      <c r="G32" s="196"/>
+      <c r="H32" s="196"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="192"/>
-      <c r="B33" s="192"/>
-      <c r="C33" s="192"/>
-      <c r="D33" s="192"/>
-      <c r="E33" s="192"/>
-      <c r="F33" s="192"/>
-      <c r="G33" s="192"/>
-      <c r="H33" s="192"/>
+      <c r="A33" s="196"/>
+      <c r="B33" s="196"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="196"/>
+      <c r="E33" s="196"/>
+      <c r="F33" s="196"/>
+      <c r="G33" s="196"/>
+      <c r="H33" s="196"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="192"/>
-      <c r="B34" s="192"/>
-      <c r="C34" s="192"/>
-      <c r="D34" s="192"/>
-      <c r="E34" s="192"/>
-      <c r="F34" s="192"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
+      <c r="A34" s="196"/>
+      <c r="B34" s="196"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="196"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="93" t="s">
@@ -10603,52 +13593,52 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="193" t="s">
+      <c r="A37" s="197" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="193"/>
-      <c r="C37" s="193"/>
-      <c r="D37" s="193"/>
-      <c r="E37" s="193"/>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
+      <c r="B37" s="197"/>
+      <c r="C37" s="197"/>
+      <c r="D37" s="197"/>
+      <c r="E37" s="197"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="193" t="s">
+      <c r="A38" s="197" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="193"/>
-      <c r="C38" s="193"/>
-      <c r="D38" s="193"/>
-      <c r="E38" s="193"/>
-      <c r="F38" s="193"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
+      <c r="B38" s="197"/>
+      <c r="C38" s="197"/>
+      <c r="D38" s="197"/>
+      <c r="E38" s="197"/>
+      <c r="F38" s="197"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="197"/>
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="193" t="s">
+      <c r="A39" s="197" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="193"/>
-      <c r="C39" s="193"/>
-      <c r="D39" s="193"/>
-      <c r="E39" s="193"/>
-      <c r="F39" s="193"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
+      <c r="B39" s="197"/>
+      <c r="C39" s="197"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="193" t="s">
+      <c r="A40" s="197" t="s">
         <v>152</v>
       </c>
-      <c r="B40" s="193"/>
-      <c r="C40" s="193"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="13">
